--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -1,23 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{D679F3BB-E391-4F43-9EBB-C81E8A56627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="TestCaseIDs">Sheet2!$B$1:$BY$1</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="134">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -232,12 +247,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698924</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>221 Recruitment (Rivel Hehyte (10216960))</t>
   </si>
   <si>
@@ -383,9 +392,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10698925</t>
   </si>
   <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
@@ -433,65 +439,65 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -503,13 +509,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,7 +526,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,31 +552,53 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -943,9 +971,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:BY36"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BY36"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -1024,7 +1052,7 @@
     <col min="77" max="77" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:77" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:77" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1257,237 +1285,232 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="L2" s="16">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="O2" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="16">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45752</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" s="10" t="s">
+      <c r="P2" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="Q2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="R2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="T2" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="S2" s="17" t="s">
+      <c r="U2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="V2" s="16">
+        <f t="shared" ref="V2:V3" ca="1" si="1">L2</f>
+        <v>45761</v>
+      </c>
+      <c r="W2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="X2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="U2" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="V2" s="16">
-        <f t="shared" ref="V2:V3" si="1">L2</f>
-        <v>45752</v>
-      </c>
-      <c r="W2" s="15" t="s">
+      <c r="Y2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="Z2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="AA2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="AB2" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AC2" s="19" t="s">
         <v>91</v>
-      </c>
-      <c r="AB2" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" s="19" t="s">
-        <v>93</v>
       </c>
       <c r="AD2" s="20">
         <v>35</v>
       </c>
       <c r="AE2" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG2" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AH2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AG2" s="22" t="s">
+      <c r="AI2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AJ2" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AK2" s="23">
+        <f t="shared" ref="AK2:AK3" ca="1" si="2">V2</f>
+        <v>45761</v>
+      </c>
+      <c r="AL2" s="23">
+        <f t="shared" ref="AL2:AL3" ca="1" si="3">V2</f>
+        <v>45761</v>
+      </c>
+      <c r="AM2" s="23">
+        <f t="shared" ref="AM2:AM3" ca="1" si="4">V2</f>
+        <v>45761</v>
+      </c>
+      <c r="AN2" s="16" t="str">
+        <f t="shared" ref="AN2:AN3" si="5">AG2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AO2" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AP2" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="AK2" s="23">
-        <f t="shared" ref="AK2:AK3" si="2">V2</f>
-        <v>45752</v>
-      </c>
-      <c r="AL2" s="23">
-        <f t="shared" ref="AL2:AL3" si="3">V2</f>
-        <v>45752</v>
-      </c>
-      <c r="AM2" s="23">
-        <f t="shared" ref="AM2:AM3" si="4">V2</f>
-        <v>45752</v>
-      </c>
-      <c r="AN2" s="16">
-        <f t="shared" ref="AN2:AN3" si="5">AG2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AQ2" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AR2" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AS2" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AT2" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AU2" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AV2" s="23">
+        <f t="shared" ref="AV2:AV3" ca="1" si="6">TODAY()+20</f>
+        <v>45812</v>
+      </c>
+      <c r="AW2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX2" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AY2" s="25" t="str">
+        <f ca="1">BB11</f>
+        <v>X6RQBABA42</v>
+      </c>
+      <c r="AZ2" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="AV2" s="23">
-        <f t="shared" ref="AV2:AV3" si="6">TODAY()+20</f>
-        <v>45803</v>
-      </c>
-      <c r="AW2" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX2" s="24" t="s">
+      <c r="BA2" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" s="25" t="str">
-        <f>BB11</f>
-        <v>X7RQBABA11</v>
-      </c>
-      <c r="AZ2" s="23" t="s">
+      <c r="BB2" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="BA2" s="23" t="s">
+      <c r="BC2" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD2" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE2" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="BF2" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="BG2" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="BB2" s="11" t="s">
+      <c r="BH2" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI2" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ2" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="BK2" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="BC2" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD2" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE2" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="BF2" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="BG2" s="27" t="s">
+      <c r="BL2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="BI2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ2" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="BK2" s="29" t="s">
+      <c r="BM2" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BN2" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="BM2" s="28" t="s">
+      <c r="BO2" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="BP2" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="BN2" s="10" t="s">
+      <c r="BQ2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="BR2" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="BO2" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="BP2" s="10" t="s">
+      <c r="BS2" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="BR2" s="10" t="s">
+      <c r="BT2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="BU2" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="BS2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="BT2" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="BU2" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="BV2" s="30">
-        <f t="array" ref="BV2:BV3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>89954</v>
+        <f t="array" aca="1" ref="BV2:BV3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <v>38861</v>
       </c>
       <c r="BW2" s="23">
         <v>44562</v>
@@ -1496,239 +1519,235 @@
         <v>47119</v>
       </c>
       <c r="BY2" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="E3" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="H3" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="I3" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="16">
+        <f t="shared" ca="1" si="0"/>
+        <v>45761</v>
+      </c>
+      <c r="M3" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="N3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="S3" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="V3" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>45761</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="X3" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="Y3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="AA3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB3" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC3" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="16">
-        <f t="shared" si="0"/>
-        <v>45752</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="S3" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="V3" s="16">
-        <f t="shared" si="1"/>
-        <v>45752</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="X3" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA3" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC3" s="19" t="s">
-        <v>128</v>
       </c>
       <c r="AD3" s="20">
         <v>35</v>
       </c>
       <c r="AE3" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="AF3" s="11" t="s">
+      <c r="AH3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AG3" s="22" t="s">
+      <c r="AI3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AH3" s="15" t="s">
+      <c r="AJ3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AI3" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
-        <v>99</v>
-      </c>
       <c r="AK3" s="23">
-        <f t="shared" si="2"/>
-        <v>45752</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45761</v>
       </c>
       <c r="AL3" s="23">
-        <f t="shared" si="3"/>
-        <v>45752</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45761</v>
       </c>
       <c r="AM3" s="23">
-        <f t="shared" si="4"/>
-        <v>45752</v>
-      </c>
-      <c r="AN3" s="16">
+        <f t="shared" ca="1" si="4"/>
+        <v>45761</v>
+      </c>
+      <c r="AN3" s="16" t="str">
         <f t="shared" si="5"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AO3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="AP3" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AQ3" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR3" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="AS3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT3" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="AU3" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV3" s="23">
+        <f t="shared" ca="1" si="6"/>
+        <v>45812</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX3" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="AY3" s="25" t="str">
+        <f ca="1">BB12</f>
+        <v>X6RQBABA59</v>
+      </c>
+      <c r="AZ3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="BA3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="BB3" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="BC3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD3" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE3" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="BF3" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="BG3" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="BH3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI3" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="BK3" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM3" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN3" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="AP3" s="15" t="s">
+      <c r="BO3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="BP3" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="BQ3" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="BR3" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="AQ3" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR3" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="AS3" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="AT3" s="10" t="s">
+      <c r="BS3" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="AU3" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV3" s="23">
-        <f t="shared" si="6"/>
-        <v>45803</v>
-      </c>
-      <c r="AW3" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX3" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY3" s="25" t="str">
-        <f>BB12</f>
-        <v>X7RQBABA34</v>
-      </c>
-      <c r="AZ3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA3" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB3" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="BC3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD3" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE3" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="BF3" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="BG3" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="BH3" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="BI3" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ3" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="BK3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL3" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="BM3" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="BN3" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="BO3" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="BP3" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="BQ3" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="BR3" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="BS3" s="10" t="s">
-        <v>134</v>
-      </c>
       <c r="BT3" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BU3" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="BV3" s="30">
-        <v>36846</v>
+        <f ca="1"/>
+        <v>30751</v>
       </c>
       <c r="BW3" s="23">
         <v>44562</v>
@@ -1737,437 +1756,461 @@
         <v>47119</v>
       </c>
       <c r="BY3" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" ht="15.65" customHeight="1" spans="3:38" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="8"/>
       <c r="AL4" s="23"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="8"/>
     </row>
-    <row r="7" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="8"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="8"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="8"/>
     </row>
-    <row r="10" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="8"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C11" s="8"/>
       <c r="AX11" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY11" s="2">
-        <f t="array" ref="AY11:AY30">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>7</v>
+        <f t="array" aca="1" ref="AY11:AY30" ca="1">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
+        <v>6</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BA11" s="2">
-        <f t="array" ref="BA11:BA30">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
-        <v>11</v>
+        <f t="array" aca="1" ref="BA11:BA30" ca="1">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
+        <v>42</v>
       </c>
       <c r="BB11" s="1" t="str">
-        <f>AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X7RQBABA11</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f ca="1">AX11&amp;AY11&amp;AZ11&amp;BA11</f>
+        <v>X6RQBABA42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C12" s="8"/>
       <c r="AX12" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY12" s="2">
-        <v>7</v>
+        <f ca="1"/>
+        <v>6</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BA12" s="2">
-        <v>34</v>
+        <f ca="1"/>
+        <v>59</v>
       </c>
       <c r="BB12" s="1" t="str">
-        <f t="shared" ref="BB12:BB36" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X7RQBABA34</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BB12:BB36" ca="1" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
+        <v>X6RQBABA59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C13" s="8"/>
       <c r="AY13" s="2">
-        <v>7</v>
+        <f ca="1"/>
+        <v>8</v>
       </c>
       <c r="BA13" s="2">
-        <v>79</v>
+        <f ca="1"/>
+        <v>73</v>
       </c>
       <c r="BB13" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>779</v>
-      </c>
-    </row>
-    <row r="14" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>873</v>
+      </c>
+    </row>
+    <row r="14" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C14" s="8"/>
       <c r="AX14" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY14" s="2">
-        <v>4</v>
+        <f ca="1"/>
+        <v>6</v>
       </c>
       <c r="BA14" s="2">
-        <v>14</v>
+        <f ca="1"/>
+        <v>41</v>
       </c>
       <c r="BB14" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X414</v>
-      </c>
-    </row>
-    <row r="15" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X641</v>
+      </c>
+    </row>
+    <row r="15" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C15" s="8"/>
       <c r="AX15" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY15" s="2">
-        <v>2</v>
+        <f ca="1"/>
+        <v>7</v>
       </c>
       <c r="BA15" s="2">
-        <v>18</v>
+        <f ca="1"/>
+        <v>31</v>
       </c>
       <c r="BB15" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X218</v>
-      </c>
-    </row>
-    <row r="16" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X731</v>
+      </c>
+    </row>
+    <row r="16" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="8"/>
       <c r="AX16" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY16" s="2">
-        <v>8</v>
+        <f ca="1"/>
+        <v>1</v>
       </c>
       <c r="BA16" s="2">
-        <v>15</v>
+        <f ca="1"/>
+        <v>18</v>
       </c>
       <c r="BB16" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X815</v>
-      </c>
-    </row>
-    <row r="17" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X118</v>
+      </c>
+    </row>
+    <row r="17" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="8"/>
       <c r="AX17" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY17" s="2">
+        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="BA17" s="2">
-        <v>63</v>
+        <f ca="1"/>
+        <v>83</v>
       </c>
       <c r="BB17" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X863</v>
-      </c>
-    </row>
-    <row r="18" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X883</v>
+      </c>
+    </row>
+    <row r="18" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C18" s="8"/>
       <c r="AX18" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY18" s="2">
-        <v>8</v>
+        <f ca="1"/>
+        <v>9</v>
       </c>
       <c r="BA18" s="2">
-        <v>44</v>
+        <f ca="1"/>
+        <v>50</v>
       </c>
       <c r="BB18" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X844</v>
-      </c>
-    </row>
-    <row r="19" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X950</v>
+      </c>
+    </row>
+    <row r="19" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19" s="8"/>
       <c r="AX19" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY19" s="2">
-        <v>8</v>
+        <f ca="1"/>
+        <v>5</v>
       </c>
       <c r="BA19" s="2">
-        <v>70</v>
+        <f ca="1"/>
+        <v>17</v>
       </c>
       <c r="BB19" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X870</v>
-      </c>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X517</v>
+      </c>
+    </row>
+    <row r="20" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="8"/>
       <c r="AX20" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY20" s="2">
-        <v>5</v>
+        <f ca="1"/>
+        <v>4</v>
       </c>
       <c r="BA20" s="2">
-        <v>21</v>
+        <f ca="1"/>
+        <v>8</v>
       </c>
       <c r="BB20" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X521</v>
-      </c>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X48</v>
+      </c>
+    </row>
+    <row r="21" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21" s="8"/>
       <c r="AX21" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY21" s="2">
-        <v>4</v>
+        <f ca="1"/>
+        <v>1</v>
       </c>
       <c r="BA21" s="2">
-        <v>39</v>
+        <f ca="1"/>
+        <v>20</v>
       </c>
       <c r="BB21" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X439</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X120</v>
+      </c>
+    </row>
+    <row r="22" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C22" s="8"/>
       <c r="AX22" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY22" s="2">
-        <v>1</v>
+        <f ca="1"/>
+        <v>4</v>
       </c>
       <c r="BA22" s="2">
-        <v>99</v>
+        <f ca="1"/>
+        <v>40</v>
       </c>
       <c r="BB22" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X199</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X440</v>
+      </c>
+    </row>
+    <row r="23" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C23" s="8"/>
       <c r="AX23" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY23" s="2">
-        <v>8</v>
+        <f ca="1"/>
+        <v>5</v>
       </c>
       <c r="BA23" s="2">
-        <v>13</v>
+        <f ca="1"/>
+        <v>61</v>
       </c>
       <c r="BB23" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X813</v>
-      </c>
-    </row>
-    <row r="24" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X561</v>
+      </c>
+    </row>
+    <row r="24" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C24" s="8"/>
       <c r="AX24" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY24" s="2">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="BA24" s="2">
-        <v>55</v>
+        <f ca="1"/>
+        <v>50</v>
       </c>
       <c r="BB24" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X455</v>
-      </c>
-    </row>
-    <row r="25" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X450</v>
+      </c>
+    </row>
+    <row r="25" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C25" s="8"/>
       <c r="AX25" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY25" s="2">
-        <v>9</v>
+        <f ca="1"/>
+        <v>1</v>
       </c>
       <c r="BA25" s="2">
-        <v>33</v>
+        <f ca="1"/>
+        <v>24</v>
       </c>
       <c r="BB25" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X933</v>
-      </c>
-    </row>
-    <row r="26" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X124</v>
+      </c>
+    </row>
+    <row r="26" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="8"/>
       <c r="AX26" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY26" s="2">
-        <v>4</v>
+        <f ca="1"/>
+        <v>5</v>
       </c>
       <c r="BA26" s="2">
-        <v>34</v>
+        <f ca="1"/>
+        <v>25</v>
       </c>
       <c r="BB26" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X434</v>
-      </c>
-    </row>
-    <row r="27" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X525</v>
+      </c>
+    </row>
+    <row r="27" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="8"/>
       <c r="AX27" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY27" s="2">
-        <v>5</v>
+        <f ca="1"/>
+        <v>7</v>
       </c>
       <c r="BA27" s="2">
-        <v>45</v>
+        <f ca="1"/>
+        <v>83</v>
       </c>
       <c r="BB27" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X545</v>
-      </c>
-    </row>
-    <row r="28" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X783</v>
+      </c>
+    </row>
+    <row r="28" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="8"/>
       <c r="AX28" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY28" s="2">
-        <v>4</v>
+        <f ca="1"/>
+        <v>3</v>
       </c>
       <c r="BA28" s="2">
-        <v>71</v>
+        <f ca="1"/>
+        <v>65</v>
       </c>
       <c r="BB28" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X471</v>
-      </c>
-    </row>
-    <row r="29" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X365</v>
+      </c>
+    </row>
+    <row r="29" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C29" s="8"/>
       <c r="AX29" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY29" s="2">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="BA29" s="2">
-        <v>63</v>
+        <f ca="1"/>
+        <v>29</v>
       </c>
       <c r="BB29" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X463</v>
-      </c>
-    </row>
-    <row r="30" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X429</v>
+      </c>
+    </row>
+    <row r="30" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="8"/>
       <c r="AX30" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AY30" s="2">
-        <v>1</v>
+        <f ca="1"/>
+        <v>7</v>
       </c>
       <c r="BA30" s="2">
-        <v>65</v>
+        <f ca="1"/>
+        <v>50</v>
       </c>
       <c r="BB30" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X165</v>
-      </c>
-    </row>
-    <row r="31" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X750</v>
+      </c>
+    </row>
+    <row r="31" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C31" s="8"/>
       <c r="AX31" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BB31" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C32" s="8"/>
       <c r="AX32" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BB32" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="8"/>
       <c r="AX33" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BB33" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C34" s="8"/>
       <c r="AX34" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BB34" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="8"/>
       <c r="AX35" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BB35" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C36" s="8"/>
-      <c r="BB36" s="1">
+      <c r="BB36" s="1" t="str">
         <f t="shared" si="7"/>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AJ3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AJ3 W2:W3 U2:U3 R2:R3 K2:K3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="T2" r:id="rId1"/>
-    <hyperlink ref="T3" r:id="rId2"/>
+    <hyperlink ref="T2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="T3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -1,38 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{D679F3BB-E391-4F43-9EBB-C81E8A56627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="TestCaseIDs">Sheet2!$B$1:$BY$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="138">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -247,6 +232,15 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Jeffry Kiehn' Employee:{undefined}TimeoutError: page.goto: Timeout 30000ms exceeded.
+Call log:
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark17/login.htmld", waiting until "load"[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>221 Recruitment (Rivel Hehyte (10216960))</t>
   </si>
   <si>
@@ -256,10 +250,10 @@
     <t>Madame</t>
   </si>
   <si>
-    <t>Geo</t>
-  </si>
-  <si>
-    <t>Weimann</t>
+    <t>Jeffry</t>
+  </si>
+  <si>
+    <t>Kiehn</t>
   </si>
   <si>
     <t>03 48 29 85 70</t>
@@ -394,16 +388,22 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10699087</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Jeremie</t>
-  </si>
-  <si>
-    <t>Jenkins</t>
-  </si>
-  <si>
-    <t>Auto 79676404</t>
+    <t>Stephania</t>
+  </si>
+  <si>
+    <t>Johnston</t>
+  </si>
+  <si>
+    <t>Auto 7665207</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -439,65 +439,65 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -509,13 +509,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -526,7 +526,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -552,53 +552,31 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -971,9 +949,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BY36"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C1:BY36"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -1052,7 +1030,7 @@
     <col min="77" max="77" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:77" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1285,231 +1263,236 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="8"/>
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="D2" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="16">
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="16">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+      <c r="N2" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="V2" s="16">
+        <f t="shared" ref="V2:V3" si="1">L2</f>
         <v>45761</v>
       </c>
-      <c r="M2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="T2" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" s="16">
-        <f t="shared" ref="V2:V3" ca="1" si="1">L2</f>
-        <v>45761</v>
-      </c>
       <c r="W2" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA2" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AB2" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC2" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AD2" s="20">
         <v>35</v>
       </c>
       <c r="AE2" s="21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AF2" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AG2" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AH2" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AI2" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ2" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK2" s="23">
+        <f t="shared" ref="AK2:AK3" si="2">V2</f>
+        <v>45761</v>
+      </c>
+      <c r="AL2" s="23">
+        <f t="shared" ref="AL2:AL3" si="3">V2</f>
+        <v>45761</v>
+      </c>
+      <c r="AM2" s="23">
+        <f t="shared" ref="AM2:AM3" si="4">V2</f>
+        <v>45761</v>
+      </c>
+      <c r="AN2" s="16">
+        <f t="shared" ref="AN2:AN3" si="5">AG2</f>
+        <v>NaN</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP2" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ2" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR2" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS2" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="AT2" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AU2" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV2" s="23">
+        <f t="shared" ref="AV2:AV3" si="6">TODAY()+20</f>
+        <v>45812</v>
+      </c>
+      <c r="AW2" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX2" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" s="25" t="str">
+        <f>BB11</f>
+        <v>X6RQBABA42</v>
+      </c>
+      <c r="AZ2" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA2" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="BB2" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="BC2" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD2" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE2" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF2" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG2" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="BH2" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AJ2" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK2" s="23">
-        <f t="shared" ref="AK2:AK3" ca="1" si="2">V2</f>
-        <v>45761</v>
-      </c>
-      <c r="AL2" s="23">
-        <f t="shared" ref="AL2:AL3" ca="1" si="3">V2</f>
-        <v>45761</v>
-      </c>
-      <c r="AM2" s="23">
-        <f t="shared" ref="AM2:AM3" ca="1" si="4">V2</f>
-        <v>45761</v>
-      </c>
-      <c r="AN2" s="16" t="str">
-        <f t="shared" ref="AN2:AN3" si="5">AG2</f>
-        <v>N/A</v>
-      </c>
-      <c r="AO2" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="AP2" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="AQ2" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="AR2" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="AS2" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AU2" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="AV2" s="23">
-        <f t="shared" ref="AV2:AV3" ca="1" si="6">TODAY()+20</f>
-        <v>45812</v>
-      </c>
-      <c r="AW2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AX2" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="AY2" s="25" t="str">
-        <f ca="1">BB11</f>
-        <v>X6RQBABA42</v>
-      </c>
-      <c r="AZ2" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="BA2" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="BB2" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="BC2" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="BD2" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="BE2" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="BF2" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="BG2" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="BH2" s="23" t="s">
-        <v>94</v>
-      </c>
       <c r="BI2" s="28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ2" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="BK2" s="29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BL2" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BM2" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BN2" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BO2" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="BP2" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BQ2" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BR2" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BS2" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BT2" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BU2" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BV2" s="30">
-        <f t="array" aca="1" ref="BV2:BV3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <f t="array" ref="BV2:BV3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
         <v>38861</v>
       </c>
       <c r="BW2" s="23">
@@ -1519,234 +1502,238 @@
         <v>47119</v>
       </c>
       <c r="BY2" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" ht="15.65" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="8"/>
+        <v>121</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="D3" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L3" s="16">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45761</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O3" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R3" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="P3" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>78</v>
-      </c>
       <c r="S3" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="T3" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U3" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="V3" s="16">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45761</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AB3" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC3" s="19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AD3" s="20">
         <v>35</v>
       </c>
       <c r="AE3" s="21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AF3" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AG3" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AH3" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AI3" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ3" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK3" s="23">
+        <f t="shared" si="2"/>
+        <v>45761</v>
+      </c>
+      <c r="AL3" s="23">
+        <f t="shared" si="3"/>
+        <v>45761</v>
+      </c>
+      <c r="AM3" s="23">
+        <f t="shared" si="4"/>
+        <v>45761</v>
+      </c>
+      <c r="AN3" s="16">
+        <f t="shared" si="5"/>
+        <v>NaN</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP3" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR3" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="AT3" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU3" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AJ3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK3" s="23">
-        <f t="shared" ca="1" si="2"/>
-        <v>45761</v>
-      </c>
-      <c r="AL3" s="23">
-        <f t="shared" ca="1" si="3"/>
-        <v>45761</v>
-      </c>
-      <c r="AM3" s="23">
-        <f t="shared" ca="1" si="4"/>
-        <v>45761</v>
-      </c>
-      <c r="AN3" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v>N/A</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ3" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="AR3" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="AS3" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT3" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU3" s="10" t="s">
-        <v>94</v>
-      </c>
       <c r="AV3" s="23">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" si="6"/>
         <v>45812</v>
       </c>
       <c r="AW3" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AX3" s="24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AY3" s="25" t="str">
-        <f ca="1">BB12</f>
+        <f>BB12</f>
         <v>X6RQBABA59</v>
       </c>
       <c r="AZ3" s="23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BA3" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BB3" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="BC3" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="BC3" s="23" t="s">
-        <v>106</v>
-      </c>
       <c r="BD3" s="26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BE3" s="26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="BF3" s="26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="BG3" s="27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BH3" s="23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BI3" s="28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ3" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="BK3" s="29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BL3" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BM3" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BN3" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BO3" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="BP3" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BQ3" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BR3" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BS3" s="10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BT3" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BU3" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BV3" s="30">
-        <f ca="1"/>
         <v>30751</v>
       </c>
       <c r="BW3" s="23">
@@ -1756,461 +1743,437 @@
         <v>47119</v>
       </c>
       <c r="BY3" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" ht="15.65" customHeight="1" spans="3:38" x14ac:dyDescent="0.25">
       <c r="C4" s="8"/>
       <c r="AL4" s="23"/>
     </row>
-    <row r="5" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" s="8"/>
     </row>
-    <row r="7" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" s="8"/>
     </row>
-    <row r="8" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C8" s="8"/>
     </row>
-    <row r="9" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C9" s="8"/>
     </row>
-    <row r="10" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C10" s="8"/>
     </row>
-    <row r="11" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C11" s="8"/>
       <c r="AX11" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY11" s="2">
-        <f t="array" aca="1" ref="AY11:AY30" ca="1">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
+        <f t="array" ref="AY11:AY30">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
         <v>6</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BA11" s="2">
-        <f t="array" aca="1" ref="BA11:BA30" ca="1">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
+        <f t="array" ref="BA11:BA30">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
         <v>42</v>
       </c>
       <c r="BB11" s="1" t="str">
-        <f ca="1">AX11&amp;AY11&amp;AZ11&amp;BA11</f>
+        <f>AX11&amp;AY11&amp;AZ11&amp;BA11</f>
         <v>X6RQBABA42</v>
       </c>
     </row>
-    <row r="12" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C12" s="8"/>
       <c r="AX12" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY12" s="2">
-        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BA12" s="2">
-        <f ca="1"/>
         <v>59</v>
       </c>
       <c r="BB12" s="1" t="str">
-        <f t="shared" ref="BB12:BB36" ca="1" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
+        <f t="shared" ref="BB12:BB36" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
         <v>X6RQBABA59</v>
       </c>
     </row>
-    <row r="13" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C13" s="8"/>
       <c r="AY13" s="2">
-        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="BA13" s="2">
-        <f ca="1"/>
         <v>73</v>
       </c>
       <c r="BB13" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>873</v>
       </c>
     </row>
-    <row r="14" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C14" s="8"/>
       <c r="AX14" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY14" s="2">
-        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="BA14" s="2">
-        <f ca="1"/>
         <v>41</v>
       </c>
       <c r="BB14" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X641</v>
       </c>
     </row>
-    <row r="15" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C15" s="8"/>
       <c r="AX15" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY15" s="2">
-        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="BA15" s="2">
-        <f ca="1"/>
         <v>31</v>
       </c>
       <c r="BB15" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X731</v>
       </c>
     </row>
-    <row r="16" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C16" s="8"/>
       <c r="AX16" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY16" s="2">
-        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="BA16" s="2">
-        <f ca="1"/>
         <v>18</v>
       </c>
       <c r="BB16" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X118</v>
       </c>
     </row>
-    <row r="17" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C17" s="8"/>
       <c r="AX17" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY17" s="2">
-        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="BA17" s="2">
-        <f ca="1"/>
         <v>83</v>
       </c>
       <c r="BB17" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X883</v>
       </c>
     </row>
-    <row r="18" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C18" s="8"/>
       <c r="AX18" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY18" s="2">
-        <f ca="1"/>
         <v>9</v>
       </c>
       <c r="BA18" s="2">
-        <f ca="1"/>
         <v>50</v>
       </c>
       <c r="BB18" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X950</v>
       </c>
     </row>
-    <row r="19" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C19" s="8"/>
       <c r="AX19" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY19" s="2">
-        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="BA19" s="2">
-        <f ca="1"/>
         <v>17</v>
       </c>
       <c r="BB19" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X517</v>
       </c>
     </row>
-    <row r="20" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C20" s="8"/>
       <c r="AX20" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY20" s="2">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="BA20" s="2">
-        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="BB20" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X48</v>
       </c>
     </row>
-    <row r="21" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C21" s="8"/>
       <c r="AX21" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY21" s="2">
-        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="BA21" s="2">
-        <f ca="1"/>
         <v>20</v>
       </c>
       <c r="BB21" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X120</v>
       </c>
     </row>
-    <row r="22" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C22" s="8"/>
       <c r="AX22" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY22" s="2">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="BA22" s="2">
-        <f ca="1"/>
         <v>40</v>
       </c>
       <c r="BB22" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X440</v>
       </c>
     </row>
-    <row r="23" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C23" s="8"/>
       <c r="AX23" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY23" s="2">
-        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="BA23" s="2">
-        <f ca="1"/>
         <v>61</v>
       </c>
       <c r="BB23" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X561</v>
       </c>
     </row>
-    <row r="24" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C24" s="8"/>
       <c r="AX24" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY24" s="2">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="BA24" s="2">
-        <f ca="1"/>
         <v>50</v>
       </c>
       <c r="BB24" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X450</v>
       </c>
     </row>
-    <row r="25" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C25" s="8"/>
       <c r="AX25" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY25" s="2">
-        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="BA25" s="2">
-        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="BB25" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X124</v>
       </c>
     </row>
-    <row r="26" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C26" s="8"/>
       <c r="AX26" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY26" s="2">
-        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="BA26" s="2">
-        <f ca="1"/>
         <v>25</v>
       </c>
       <c r="BB26" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X525</v>
       </c>
     </row>
-    <row r="27" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C27" s="8"/>
       <c r="AX27" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY27" s="2">
-        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="BA27" s="2">
-        <f ca="1"/>
         <v>83</v>
       </c>
       <c r="BB27" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X783</v>
       </c>
     </row>
-    <row r="28" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C28" s="8"/>
       <c r="AX28" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY28" s="2">
-        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="BA28" s="2">
-        <f ca="1"/>
         <v>65</v>
       </c>
       <c r="BB28" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X365</v>
       </c>
     </row>
-    <row r="29" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C29" s="8"/>
       <c r="AX29" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY29" s="2">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="BA29" s="2">
-        <f ca="1"/>
         <v>29</v>
       </c>
       <c r="BB29" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X429</v>
       </c>
     </row>
-    <row r="30" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C30" s="8"/>
       <c r="AX30" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AY30" s="2">
-        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="BA30" s="2">
-        <f ca="1"/>
         <v>50</v>
       </c>
       <c r="BB30" s="1" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>X750</v>
       </c>
     </row>
-    <row r="31" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C31" s="8"/>
       <c r="AX31" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BB31" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="32" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C32" s="8"/>
       <c r="AX32" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BB32" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="33" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C33" s="8"/>
       <c r="AX33" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BB33" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="34" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C34" s="8"/>
       <c r="AX34" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BB34" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="35" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C35" s="8"/>
       <c r="AX35" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BB35" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="36" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C36" s="8"/>
-      <c r="BB36" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+      <c r="BB36" s="1">
+        <f t="shared" si="7"/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AJ3 W2:W3 U2:U3 R2:R3 K2:K3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AJ3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="T2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="T3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="T2" r:id="rId1"/>
+    <hyperlink ref="T3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -232,7 +232,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698924</t>
+    <t>10699319</t>
   </si>
   <si>
     <t>Passed</t>
@@ -247,10 +247,10 @@
     <t>Madame</t>
   </si>
   <si>
-    <t>Geo</t>
-  </si>
-  <si>
-    <t>Weimann</t>
+    <t>Orpha</t>
+  </si>
+  <si>
+    <t>Schmitt</t>
   </si>
   <si>
     <t>03 48 29 85 70</t>
@@ -385,19 +385,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10698925</t>
+    <t>10699087</t>
   </si>
   <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Jeremie</t>
-  </si>
-  <si>
-    <t>Jenkins</t>
-  </si>
-  <si>
-    <t>Auto 79676404</t>
+    <t>Stephania</t>
+  </si>
+  <si>
+    <t>Johnston</t>
+  </si>
+  <si>
+    <t>Auto 7665207</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -577,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -597,6 +597,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -996,7 +999,7 @@
     <col min="48" max="48" width="22" style="1" customWidth="1"/>
     <col min="49" max="49" width="11.26953125" style="1" customWidth="1"/>
     <col min="50" max="50" width="19.81640625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="16.26953125" style="2" customWidth="1"/>
+    <col min="51" max="51" width="25.90625" style="2" customWidth="1"/>
     <col min="52" max="52" width="13.90625" style="1" customWidth="1"/>
     <col min="53" max="53" width="17.6328125" style="2" customWidth="1"/>
     <col min="54" max="54" width="9.453125" style="1" customWidth="1"/>
@@ -1261,241 +1264,241 @@
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="17">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45752</v>
-      </c>
-      <c r="M2" s="10" t="s">
+        <v>45768</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="U2" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="16">
+      <c r="V2" s="17">
         <f t="shared" ref="V2:V3" si="1">L2</f>
-        <v>45752</v>
-      </c>
-      <c r="W2" s="15" t="s">
+        <v>45768</v>
+      </c>
+      <c r="W2" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="Z2" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="19" t="s">
+      <c r="AB2" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AC2" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="20">
+      <c r="AD2" s="21">
         <v>35</v>
       </c>
-      <c r="AE2" s="21" t="s">
+      <c r="AE2" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AF2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AG2" s="22" t="s">
+      <c r="AG2" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AJ2" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AK2" s="23">
+      <c r="AK2" s="24">
         <f t="shared" ref="AK2:AK3" si="2">V2</f>
-        <v>45752</v>
-      </c>
-      <c r="AL2" s="23">
+        <v>45768</v>
+      </c>
+      <c r="AL2" s="24">
         <f t="shared" ref="AL2:AL3" si="3">V2</f>
-        <v>45752</v>
-      </c>
-      <c r="AM2" s="23">
+        <v>45768</v>
+      </c>
+      <c r="AM2" s="24">
         <f t="shared" ref="AM2:AM3" si="4">V2</f>
-        <v>45752</v>
-      </c>
-      <c r="AN2" s="16">
+        <v>45768</v>
+      </c>
+      <c r="AN2" s="17">
         <f t="shared" ref="AN2:AN3" si="5">AG2</f>
         <v>NaN</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AO2" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AP2" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AQ2" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AR2" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AS2" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AT2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AU2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AV2" s="23">
+      <c r="AV2" s="24">
         <f t="shared" ref="AV2:AV3" si="6">TODAY()+20</f>
-        <v>45803</v>
-      </c>
-      <c r="AW2" s="10" t="s">
+        <v>45819</v>
+      </c>
+      <c r="AW2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AX2" s="24" t="s">
+      <c r="AX2" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" s="25" t="str">
+      <c r="AY2" s="26" t="str">
         <f>BB11</f>
-        <v>X7RQBABA11</v>
-      </c>
-      <c r="AZ2" s="23" t="s">
+        <v>X4RQBABA7</v>
+      </c>
+      <c r="AZ2" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="BA2" s="23" t="s">
+      <c r="BA2" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="BB2" s="11" t="s">
+      <c r="BB2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="BC2" s="23" t="s">
+      <c r="BC2" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="BD2" s="26" t="s">
+      <c r="BD2" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="BE2" s="26" t="s">
+      <c r="BE2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="BF2" s="26" t="s">
+      <c r="BF2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="BG2" s="27" t="s">
+      <c r="BG2" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="23" t="s">
+      <c r="BH2" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="BI2" s="28" t="s">
+      <c r="BI2" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="BJ2" s="10" t="s">
+      <c r="BJ2" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="BK2" s="29" t="s">
+      <c r="BK2" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BL2" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="BM2" s="28" t="s">
+      <c r="BM2" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="BN2" s="10" t="s">
+      <c r="BN2" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="BO2" s="10" t="s">
+      <c r="BO2" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="BP2" s="10" t="s">
+      <c r="BP2" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="10" t="s">
+      <c r="BQ2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="BR2" s="10" t="s">
+      <c r="BR2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="BS2" s="10" t="s">
+      <c r="BS2" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="BT2" s="10" t="s">
+      <c r="BT2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="BU2" s="10" t="s">
+      <c r="BU2" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="BV2" s="30">
+      <c r="BV2" s="31">
         <f t="array" ref="BV2:BV3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>89954</v>
-      </c>
-      <c r="BW2" s="23">
+        <v>69257</v>
+      </c>
+      <c r="BW2" s="24">
         <v>44562</v>
       </c>
-      <c r="BX2" s="23">
+      <c r="BX2" s="24">
         <v>47119</v>
       </c>
-      <c r="BY2" s="15" t="s">
+      <c r="BY2" s="16" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1506,331 +1509,331 @@
       <c r="B3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="17">
         <f t="shared" si="0"/>
-        <v>45752</v>
-      </c>
-      <c r="M3" s="10" t="s">
+        <v>45768</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="T3" s="18" t="s">
+      <c r="T3" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="U3" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="V3" s="16">
+      <c r="V3" s="17">
         <f t="shared" si="1"/>
-        <v>45752</v>
-      </c>
-      <c r="W3" s="15" t="s">
+        <v>45768</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="12" t="s">
+      <c r="X3" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="Y3" s="11" t="s">
+      <c r="Y3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="Z3" s="11" t="s">
+      <c r="Z3" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="AA3" s="11" t="s">
+      <c r="AA3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AB3" s="19" t="s">
+      <c r="AB3" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="AC3" s="19" t="s">
+      <c r="AC3" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="AD3" s="20">
+      <c r="AD3" s="21">
         <v>35</v>
       </c>
-      <c r="AE3" s="21" t="s">
+      <c r="AE3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="AF3" s="11" t="s">
+      <c r="AF3" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AG3" s="22" t="s">
+      <c r="AG3" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AH3" s="15" t="s">
+      <c r="AH3" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AI3" s="15" t="s">
+      <c r="AI3" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="AJ3" s="15" t="s">
+      <c r="AJ3" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AK3" s="23">
+      <c r="AK3" s="24">
         <f t="shared" si="2"/>
-        <v>45752</v>
-      </c>
-      <c r="AL3" s="23">
+        <v>45768</v>
+      </c>
+      <c r="AL3" s="24">
         <f t="shared" si="3"/>
-        <v>45752</v>
-      </c>
-      <c r="AM3" s="23">
+        <v>45768</v>
+      </c>
+      <c r="AM3" s="24">
         <f t="shared" si="4"/>
-        <v>45752</v>
-      </c>
-      <c r="AN3" s="16">
+        <v>45768</v>
+      </c>
+      <c r="AN3" s="17">
         <f t="shared" si="5"/>
         <v>NaN</v>
       </c>
-      <c r="AO3" s="15" t="s">
+      <c r="AO3" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AP3" s="15" t="s">
+      <c r="AP3" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="AQ3" s="15" t="s">
+      <c r="AQ3" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="AR3" s="15" t="s">
+      <c r="AR3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AS3" s="15" t="s">
+      <c r="AS3" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="10" t="s">
+      <c r="AT3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="AU3" s="10" t="s">
+      <c r="AU3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AV3" s="23">
+      <c r="AV3" s="24">
         <f t="shared" si="6"/>
-        <v>45803</v>
-      </c>
-      <c r="AW3" s="10" t="s">
+        <v>45819</v>
+      </c>
+      <c r="AW3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AX3" s="24" t="s">
+      <c r="AX3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="AY3" s="25" t="str">
+      <c r="AY3" s="26" t="str">
         <f>BB12</f>
-        <v>X7RQBABA34</v>
-      </c>
-      <c r="AZ3" s="23" t="s">
+        <v>X8RQBABA33</v>
+      </c>
+      <c r="AZ3" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="BA3" s="23" t="s">
+      <c r="BA3" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="BB3" s="11" t="s">
+      <c r="BB3" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="BC3" s="23" t="s">
+      <c r="BC3" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="BD3" s="26" t="s">
+      <c r="BD3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="BE3" s="26" t="s">
+      <c r="BE3" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="BF3" s="26" t="s">
+      <c r="BF3" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="BG3" s="27" t="s">
+      <c r="BG3" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="23" t="s">
+      <c r="BH3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="BI3" s="28" t="s">
+      <c r="BI3" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="BJ3" s="10" t="s">
+      <c r="BJ3" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="BK3" s="29" t="s">
+      <c r="BK3" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="BL3" s="10" t="s">
+      <c r="BL3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="BM3" s="28" t="s">
+      <c r="BM3" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="BN3" s="10" t="s">
+      <c r="BN3" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="BO3" s="10" t="s">
+      <c r="BO3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="BP3" s="10" t="s">
+      <c r="BP3" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="BQ3" s="10" t="s">
+      <c r="BQ3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="BR3" s="10" t="s">
+      <c r="BR3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="BS3" s="10" t="s">
+      <c r="BS3" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="BT3" s="10" t="s">
+      <c r="BT3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="BU3" s="10" t="s">
+      <c r="BU3" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="BV3" s="30">
-        <v>36846</v>
-      </c>
-      <c r="BW3" s="23">
+      <c r="BV3" s="31">
+        <v>87332</v>
+      </c>
+      <c r="BW3" s="24">
         <v>44562</v>
       </c>
-      <c r="BX3" s="23">
+      <c r="BX3" s="24">
         <v>47119</v>
       </c>
-      <c r="BY3" s="15" t="s">
+      <c r="BY3" s="16" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4" ht="15.65" customHeight="1" spans="3:38" x14ac:dyDescent="0.25">
-      <c r="C4" s="8"/>
-      <c r="AL4" s="23"/>
+      <c r="C4" s="9"/>
+      <c r="AL4" s="24"/>
     </row>
     <row r="5" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C6" s="8"/>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" s="8"/>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C8" s="8"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C9" s="8"/>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C10" s="8"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C11" s="8"/>
+      <c r="C11" s="9"/>
       <c r="AX11" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AY11" s="2">
         <f t="array" ref="AY11:AY30">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ11" s="1" t="s">
         <v>136</v>
       </c>
       <c r="BA11" s="2">
         <f t="array" ref="BA11:BA30">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BB11" s="1" t="str">
         <f>AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X7RQBABA11</v>
+        <v>X4RQBABA7</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C12" s="8"/>
+      <c r="C12" s="9"/>
       <c r="AX12" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AY12" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ12" s="1" t="s">
         <v>136</v>
       </c>
       <c r="BA12" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="BB12" s="1" t="str">
         <f t="shared" ref="BB12:BB36" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X7RQBABA34</v>
+        <v>X8RQBABA33</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C13" s="8"/>
+      <c r="C13" s="9"/>
       <c r="AY13" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA13" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="BB13" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>779</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C14" s="8"/>
+      <c r="C14" s="9"/>
       <c r="AX14" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AY14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA14" s="2">
         <v>14</v>
       </c>
       <c r="BB14" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X414</v>
+        <v>X314</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
+      <c r="C15" s="9"/>
       <c r="AX15" s="1" t="s">
         <v>135</v>
       </c>
@@ -1838,63 +1841,63 @@
         <v>2</v>
       </c>
       <c r="BA15" s="2">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="BB15" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X218</v>
+        <v>X269</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
+      <c r="C16" s="9"/>
       <c r="AX16" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AY16" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA16" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BB16" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X815</v>
+        <v>X424</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
+      <c r="C17" s="9"/>
       <c r="AX17" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AY17" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BA17" s="2">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="BB17" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X863</v>
+        <v>X13</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C18" s="8"/>
+      <c r="C18" s="9"/>
       <c r="AX18" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AY18" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA18" s="2">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="BB18" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X844</v>
+        <v>X664</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C19" s="8"/>
+      <c r="C19" s="9"/>
       <c r="AX19" s="1" t="s">
         <v>135</v>
       </c>
@@ -1902,191 +1905,191 @@
         <v>8</v>
       </c>
       <c r="BA19" s="2">
+        <v>45</v>
+      </c>
+      <c r="BB19" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X845</v>
+      </c>
+    </row>
+    <row r="20" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C20" s="9"/>
+      <c r="AX20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY20" s="2">
+        <v>2</v>
+      </c>
+      <c r="BA20" s="2">
         <v>70</v>
       </c>
-      <c r="BB19" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X870</v>
-      </c>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C20" s="8"/>
-      <c r="AX20" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY20" s="2">
+      <c r="BB20" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X270</v>
+      </c>
+    </row>
+    <row r="21" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C21" s="9"/>
+      <c r="AX21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY21" s="2">
+        <v>8</v>
+      </c>
+      <c r="BA21" s="2">
+        <v>63</v>
+      </c>
+      <c r="BB21" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X863</v>
+      </c>
+    </row>
+    <row r="22" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C22" s="9"/>
+      <c r="AX22" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY22" s="2">
+        <v>4</v>
+      </c>
+      <c r="BA22" s="2">
+        <v>53</v>
+      </c>
+      <c r="BB22" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X453</v>
+      </c>
+    </row>
+    <row r="23" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C23" s="9"/>
+      <c r="AX23" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY23" s="2">
+        <v>9</v>
+      </c>
+      <c r="BA23" s="2">
+        <v>79</v>
+      </c>
+      <c r="BB23" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X979</v>
+      </c>
+    </row>
+    <row r="24" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C24" s="9"/>
+      <c r="AX24" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY24" s="2">
+        <v>2</v>
+      </c>
+      <c r="BA24" s="2">
+        <v>36</v>
+      </c>
+      <c r="BB24" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X236</v>
+      </c>
+    </row>
+    <row r="25" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C25" s="9"/>
+      <c r="AX25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY25" s="2">
+        <v>3</v>
+      </c>
+      <c r="BA25" s="2">
+        <v>51</v>
+      </c>
+      <c r="BB25" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X351</v>
+      </c>
+    </row>
+    <row r="26" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C26" s="9"/>
+      <c r="AX26" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY26" s="2">
         <v>5</v>
       </c>
-      <c r="BA20" s="2">
-        <v>21</v>
-      </c>
-      <c r="BB20" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X521</v>
-      </c>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C21" s="8"/>
-      <c r="AX21" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY21" s="2">
-        <v>4</v>
-      </c>
-      <c r="BA21" s="2">
-        <v>39</v>
-      </c>
-      <c r="BB21" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X439</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C22" s="8"/>
-      <c r="AX22" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY22" s="2">
+      <c r="BA26" s="2">
+        <v>65</v>
+      </c>
+      <c r="BB26" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X565</v>
+      </c>
+    </row>
+    <row r="27" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C27" s="9"/>
+      <c r="AX27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY27" s="2">
+        <v>9</v>
+      </c>
+      <c r="BA27" s="2">
+        <v>68</v>
+      </c>
+      <c r="BB27" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X968</v>
+      </c>
+    </row>
+    <row r="28" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C28" s="9"/>
+      <c r="AX28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY28" s="2">
+        <v>7</v>
+      </c>
+      <c r="BA28" s="2">
+        <v>59</v>
+      </c>
+      <c r="BB28" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X759</v>
+      </c>
+    </row>
+    <row r="29" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C29" s="9"/>
+      <c r="AX29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY29" s="2">
         <v>1</v>
       </c>
-      <c r="BA22" s="2">
-        <v>99</v>
-      </c>
-      <c r="BB22" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X199</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C23" s="8"/>
-      <c r="AX23" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY23" s="2">
-        <v>8</v>
-      </c>
-      <c r="BA23" s="2">
-        <v>13</v>
-      </c>
-      <c r="BB23" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X813</v>
-      </c>
-    </row>
-    <row r="24" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C24" s="8"/>
-      <c r="AX24" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY24" s="2">
-        <v>4</v>
-      </c>
-      <c r="BA24" s="2">
-        <v>55</v>
-      </c>
-      <c r="BB24" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X455</v>
-      </c>
-    </row>
-    <row r="25" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C25" s="8"/>
-      <c r="AX25" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY25" s="2">
-        <v>9</v>
-      </c>
-      <c r="BA25" s="2">
-        <v>33</v>
-      </c>
-      <c r="BB25" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X933</v>
-      </c>
-    </row>
-    <row r="26" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C26" s="8"/>
-      <c r="AX26" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY26" s="2">
-        <v>4</v>
-      </c>
-      <c r="BA26" s="2">
-        <v>34</v>
-      </c>
-      <c r="BB26" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X434</v>
-      </c>
-    </row>
-    <row r="27" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C27" s="8"/>
-      <c r="AX27" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY27" s="2">
+      <c r="BA29" s="2">
+        <v>81</v>
+      </c>
+      <c r="BB29" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>X181</v>
+      </c>
+    </row>
+    <row r="30" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="C30" s="9"/>
+      <c r="AX30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY30" s="2">
         <v>5</v>
       </c>
-      <c r="BA27" s="2">
-        <v>45</v>
-      </c>
-      <c r="BB27" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X545</v>
-      </c>
-    </row>
-    <row r="28" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C28" s="8"/>
-      <c r="AX28" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY28" s="2">
-        <v>4</v>
-      </c>
-      <c r="BA28" s="2">
-        <v>71</v>
-      </c>
-      <c r="BB28" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X471</v>
-      </c>
-    </row>
-    <row r="29" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C29" s="8"/>
-      <c r="AX29" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY29" s="2">
-        <v>4</v>
-      </c>
-      <c r="BA29" s="2">
-        <v>63</v>
-      </c>
-      <c r="BB29" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X463</v>
-      </c>
-    </row>
-    <row r="30" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C30" s="8"/>
-      <c r="AX30" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY30" s="2">
-        <v>1</v>
-      </c>
       <c r="BA30" s="2">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="BB30" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X165</v>
+        <v>X549</v>
       </c>
     </row>
     <row r="31" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C31" s="8"/>
+      <c r="C31" s="9"/>
       <c r="AX31" s="1" t="s">
         <v>135</v>
       </c>
@@ -2096,7 +2099,7 @@
       </c>
     </row>
     <row r="32" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C32" s="8"/>
+      <c r="C32" s="9"/>
       <c r="AX32" s="1" t="s">
         <v>135</v>
       </c>
@@ -2106,7 +2109,7 @@
       </c>
     </row>
     <row r="33" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C33" s="8"/>
+      <c r="C33" s="9"/>
       <c r="AX33" s="1" t="s">
         <v>135</v>
       </c>
@@ -2116,7 +2119,7 @@
       </c>
     </row>
     <row r="34" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C34" s="8"/>
+      <c r="C34" s="9"/>
       <c r="AX34" s="1" t="s">
         <v>135</v>
       </c>
@@ -2126,7 +2129,7 @@
       </c>
     </row>
     <row r="35" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C35" s="8"/>
+      <c r="C35" s="9"/>
       <c r="AX35" s="1" t="s">
         <v>135</v>
       </c>
@@ -2136,7 +2139,7 @@
       </c>
     </row>
     <row r="36" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
+      <c r="C36" s="9"/>
       <c r="BB36" s="1">
         <f t="shared" si="7"/>
       </c>

--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="137">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -232,13 +232,10 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Jeffry Kiehn' Employee:{undefined}TimeoutError: page.goto: Timeout 30000ms exceeded.
-Call log:
-  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark17/login.htmld", waiting until "load"[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>10699520</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>221 Recruitment (Rivel Hehyte (10216960))</t>
@@ -250,10 +247,10 @@
     <t>Madame</t>
   </si>
   <si>
-    <t>Jeffry</t>
-  </si>
-  <si>
-    <t>Kiehn</t>
+    <t>Carolanne</t>
+  </si>
+  <si>
+    <t>Hilpert</t>
   </si>
   <si>
     <t>03 48 29 85 70</t>
@@ -388,22 +385,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699087</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>10699526</t>
   </si>
   <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Stephania</t>
-  </si>
-  <si>
-    <t>Johnston</t>
-  </si>
-  <si>
-    <t>Auto 7665207</t>
+    <t>Blake</t>
+  </si>
+  <si>
+    <t>Trantow</t>
+  </si>
+  <si>
+    <t>Auto 1854189</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -583,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -669,6 +663,9 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1002,7 +999,7 @@
     <col min="48" max="48" width="22" style="1" customWidth="1"/>
     <col min="49" max="49" width="11.26953125" style="1" customWidth="1"/>
     <col min="50" max="50" width="19.81640625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="16.26953125" style="2" customWidth="1"/>
+    <col min="51" max="51" width="32.54296875" style="2" customWidth="1"/>
     <col min="52" max="52" width="13.90625" style="1" customWidth="1"/>
     <col min="53" max="53" width="17.6328125" style="2" customWidth="1"/>
     <col min="54" max="54" width="9.453125" style="1" customWidth="1"/>
@@ -1299,7 +1296,7 @@
       </c>
       <c r="L2" s="16">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>74</v>
@@ -1330,7 +1327,7 @@
       </c>
       <c r="V2" s="16">
         <f t="shared" ref="V2:V3" si="1">L2</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="W2" s="15" t="s">
         <v>87</v>
@@ -1376,15 +1373,15 @@
       </c>
       <c r="AK2" s="23">
         <f t="shared" ref="AK2:AK3" si="2">V2</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AL2" s="23">
         <f t="shared" ref="AL2:AL3" si="3">V2</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AM2" s="23">
         <f t="shared" ref="AM2:AM3" si="4">V2</f>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AN2" s="16">
         <f t="shared" ref="AN2:AN3" si="5">AG2</f>
@@ -1413,7 +1410,7 @@
       </c>
       <c r="AV2" s="23">
         <f t="shared" ref="AV2:AV3" si="6">TODAY()+20</f>
-        <v>45812</v>
+        <v>45830</v>
       </c>
       <c r="AW2" s="10" t="s">
         <v>74</v>
@@ -1423,7 +1420,7 @@
       </c>
       <c r="AY2" s="25" t="str">
         <f>BB11</f>
-        <v>X6RQBABA42</v>
+        <v>X4RQBABA57</v>
       </c>
       <c r="AZ2" s="23" t="s">
         <v>108</v>
@@ -1493,7 +1490,7 @@
       </c>
       <c r="BV2" s="30">
         <f t="array" ref="BV2:BV3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>38861</v>
+        <v>69719</v>
       </c>
       <c r="BW2" s="23">
         <v>44562</v>
@@ -1509,14 +1506,14 @@
       <c r="A3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="31" t="s">
         <v>122</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>74</v>
@@ -1525,10 +1522,10 @@
         <v>75</v>
       </c>
       <c r="G3" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>125</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>126</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>78</v>
@@ -1541,7 +1538,7 @@
       </c>
       <c r="L3" s="16">
         <f t="shared" si="0"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>74</v>
@@ -1572,19 +1569,19 @@
       </c>
       <c r="V3" s="16">
         <f t="shared" si="1"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="W3" s="15" t="s">
         <v>87</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y3" s="11" t="s">
         <v>89</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA3" s="11" t="s">
         <v>91</v>
@@ -1593,7 +1590,7 @@
         <v>92</v>
       </c>
       <c r="AC3" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AD3" s="20">
         <v>35</v>
@@ -1618,25 +1615,25 @@
       </c>
       <c r="AK3" s="23">
         <f t="shared" si="2"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AL3" s="23">
         <f t="shared" si="3"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AM3" s="23">
         <f t="shared" si="4"/>
-        <v>45761</v>
+        <v>45779</v>
       </c>
       <c r="AN3" s="16">
         <f t="shared" si="5"/>
         <v>NaN</v>
       </c>
       <c r="AO3" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP3" s="15" t="s">
         <v>130</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>131</v>
       </c>
       <c r="AQ3" s="15" t="s">
         <v>102</v>
@@ -1648,14 +1645,14 @@
         <v>104</v>
       </c>
       <c r="AT3" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AU3" s="10" t="s">
         <v>96</v>
       </c>
       <c r="AV3" s="23">
         <f t="shared" si="6"/>
-        <v>45812</v>
+        <v>45830</v>
       </c>
       <c r="AW3" s="10" t="s">
         <v>74</v>
@@ -1665,7 +1662,7 @@
       </c>
       <c r="AY3" s="25" t="str">
         <f>BB12</f>
-        <v>X6RQBABA59</v>
+        <v>X5RQBABA24</v>
       </c>
       <c r="AZ3" s="23" t="s">
         <v>108</v>
@@ -1710,7 +1707,7 @@
         <v>114</v>
       </c>
       <c r="BN3" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BO3" s="10" t="s">
         <v>75</v>
@@ -1722,10 +1719,10 @@
         <v>74</v>
       </c>
       <c r="BR3" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="BS3" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="BS3" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="BT3" s="10" t="s">
         <v>74</v>
@@ -1734,7 +1731,7 @@
         <v>119</v>
       </c>
       <c r="BV3" s="30">
-        <v>30751</v>
+        <v>29819</v>
       </c>
       <c r="BW3" s="23">
         <v>44562</v>
@@ -1769,332 +1766,332 @@
     <row r="11" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C11" s="8"/>
       <c r="AX11" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY11" s="2">
         <f t="array" ref="AY11:AY30">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BA11" s="2">
         <f t="array" ref="BA11:BA30">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="BB11" s="1" t="str">
         <f>AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X6RQBABA42</v>
+        <v>X4RQBABA57</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C12" s="8"/>
       <c r="AX12" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY12" s="2">
+        <v>5</v>
+      </c>
+      <c r="AZ12" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AY12" s="2">
-        <v>6</v>
-      </c>
-      <c r="AZ12" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="BA12" s="2">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="BB12" s="1" t="str">
         <f t="shared" ref="BB12:BB36" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X6RQBABA59</v>
+        <v>X5RQBABA24</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C13" s="8"/>
       <c r="AY13" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA13" s="2">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="BB13" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>873</v>
+        <v>932</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C14" s="8"/>
       <c r="AX14" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY14" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA14" s="2">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="BB14" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X641</v>
+        <v>X585</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C15" s="8"/>
       <c r="AX15" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY15" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA15" s="2">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="BB15" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X731</v>
+        <v>X970</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C16" s="8"/>
       <c r="AX16" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY16" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BA16" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BB16" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X118</v>
+        <v>X725</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C17" s="8"/>
       <c r="AX17" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY17" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA17" s="2">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="BB17" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X883</v>
+        <v>X958</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C18" s="8"/>
       <c r="AX18" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY18" s="2">
         <v>9</v>
       </c>
       <c r="BA18" s="2">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="BB18" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X950</v>
+        <v>X983</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C19" s="8"/>
       <c r="AX19" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY19" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA19" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="BB19" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X517</v>
+        <v>X790</v>
       </c>
     </row>
     <row r="20" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C20" s="8"/>
       <c r="AX20" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY20" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA20" s="2">
         <v>8</v>
       </c>
       <c r="BB20" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X48</v>
+        <v>X78</v>
       </c>
     </row>
     <row r="21" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C21" s="8"/>
       <c r="AX21" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY21" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BA21" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="BB21" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X120</v>
+        <v>X889</v>
       </c>
     </row>
     <row r="22" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C22" s="8"/>
       <c r="AX22" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY22" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA22" s="2">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="BB22" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X440</v>
+        <v>X78</v>
       </c>
     </row>
     <row r="23" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C23" s="8"/>
       <c r="AX23" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA23" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="BB23" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X561</v>
+        <v>X658</v>
       </c>
     </row>
     <row r="24" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C24" s="8"/>
       <c r="AX24" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY24" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BA24" s="2">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="BB24" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X450</v>
+        <v>X978</v>
       </c>
     </row>
     <row r="25" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C25" s="8"/>
       <c r="AX25" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY25" s="2">
         <v>1</v>
       </c>
       <c r="BA25" s="2">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="BB25" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X124</v>
+        <v>X189</v>
       </c>
     </row>
     <row r="26" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C26" s="8"/>
       <c r="AX26" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY26" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BA26" s="2">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BB26" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X525</v>
+        <v>X140</v>
       </c>
     </row>
     <row r="27" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C27" s="8"/>
       <c r="AX27" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY27" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BA27" s="2">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="BB27" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X783</v>
+        <v>X251</v>
       </c>
     </row>
     <row r="28" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C28" s="8"/>
       <c r="AX28" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY28" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA28" s="2">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="BB28" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X365</v>
+        <v>X522</v>
       </c>
     </row>
     <row r="29" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C29" s="8"/>
       <c r="AX29" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY29" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA29" s="2">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BB29" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X429</v>
+        <v>X565</v>
       </c>
     </row>
     <row r="30" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C30" s="8"/>
       <c r="AX30" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY30" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BA30" s="2">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="BB30" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X750</v>
+        <v>X177</v>
       </c>
     </row>
     <row r="31" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C31" s="8"/>
       <c r="AX31" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BB31" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2104,7 +2101,7 @@
     <row r="32" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C32" s="8"/>
       <c r="AX32" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BB32" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2114,7 +2111,7 @@
     <row r="33" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C33" s="8"/>
       <c r="AX33" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BB33" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2124,7 +2121,7 @@
     <row r="34" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C34" s="8"/>
       <c r="AX34" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BB34" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2134,7 +2131,7 @@
     <row r="35" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
       <c r="C35" s="8"/>
       <c r="AX35" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BB35" s="1" t="str">
         <f t="shared" si="7"/>

--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="138">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -232,172 +232,547 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699520</t>
+    <t xml:space="preserve">Test failed for 'Elijah Ebert' Employee:{10699679}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-id=\'pex-search-result-header\']//a[contains(text(),\'10699679\')])[1]')[22m
+[2m  -   locator resolved to &lt;a data-uxi-rank="0" class="pexsearch-11mf54b" data…&gt;Elijah Ebert (10699679)&lt;/a&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>221 Recruitment (Rivel Hehyte (10216960))</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Madame</t>
+  </si>
+  <si>
+    <t>Elijah</t>
+  </si>
+  <si>
+    <t>Ebert</t>
+  </si>
+  <si>
+    <t>03 48 29 85 70</t>
+  </si>
+  <si>
+    <t>Landline</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Nord-Pas-de-Calais</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>59700</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>Test@email.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Retail Assistant</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>221 Paris-Villeneuve La Garenne</t>
+  </si>
+  <si>
+    <t>Hourly</t>
+  </si>
+  <si>
+    <t>Employe@5 - Jeudi - (Contracted Days of the Week (France)-France)</t>
+  </si>
+  <si>
+    <t>5 jours (France)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>CDI (Permanent)</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>CDI (Aucune raison nécessaire)</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>Collective Agreement - France</t>
+  </si>
+  <si>
+    <t>Agent de Maîtrise</t>
+  </si>
+  <si>
+    <t>AM1</t>
+  </si>
+  <si>
+    <t>France Retail Assistant &gt;=1yr Exp</t>
+  </si>
+  <si>
+    <t>1yr Exp. or Diploma</t>
+  </si>
+  <si>
+    <t>National Identity Card (CNI)</t>
+  </si>
+  <si>
+    <t>01/01/1999</t>
+  </si>
+  <si>
+    <t>01/01/2045</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Celibataire</t>
+  </si>
+  <si>
+    <t>BNPAFRPPTAS</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>FR1420041010050500013M02606</t>
+  </si>
+  <si>
+    <t>GrunB FrunB</t>
+  </si>
+  <si>
+    <t>Maiden</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>Senger</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>FR Monthly</t>
+  </si>
+  <si>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t>10699606</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>221 Recruitment (Rivel Hehyte (10216960))</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Madame</t>
-  </si>
-  <si>
-    <t>Carolanne</t>
-  </si>
-  <si>
-    <t>Hilpert</t>
-  </si>
-  <si>
-    <t>03 48 29 85 70</t>
-  </si>
-  <si>
-    <t>Landline</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Nord-Pas-de-Calais</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>59700</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>Test@email.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Retail Assistant</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>221 Paris-Villeneuve La Garenne</t>
-  </si>
-  <si>
-    <t>Hourly</t>
-  </si>
-  <si>
-    <t>Employe@5 - Jeudi - (Contracted Days of the Week (France)-France)</t>
-  </si>
-  <si>
-    <t>5 jours (France)</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>CDI (Permanent)</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>CDI (Aucune raison nécessaire)</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>Collective Agreement - France</t>
-  </si>
-  <si>
-    <t>Agent de Maîtrise</t>
-  </si>
-  <si>
-    <t>AM1</t>
-  </si>
-  <si>
-    <t>France Retail Assistant &gt;=1yr Exp</t>
-  </si>
-  <si>
-    <t>1yr Exp. or Diploma</t>
-  </si>
-  <si>
-    <t>National Identity Card (CNI)</t>
-  </si>
-  <si>
-    <t>01/01/1999</t>
-  </si>
-  <si>
-    <t>01/01/2045</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Celibataire</t>
-  </si>
-  <si>
-    <t>BNPAFRPPTAS</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>FR1420041010050500013M02606</t>
-  </si>
-  <si>
-    <t>GrunB FrunB</t>
-  </si>
-  <si>
-    <t>Maiden</t>
-  </si>
-  <si>
-    <t>Anthony</t>
-  </si>
-  <si>
-    <t>Senger</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>FR Monthly</t>
-  </si>
-  <si>
-    <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699526</t>
-  </si>
-  <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Blake</t>
-  </si>
-  <si>
-    <t>Trantow</t>
-  </si>
-  <si>
-    <t>Auto 1854189</t>
+    <t>Eldora</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>Auto 75590546</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -515,18 +890,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,7 +952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -598,7 +973,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -608,11 +989,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -643,7 +1024,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -661,11 +1042,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1247,7 +1625,7 @@
       <c r="BU1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="BV1" s="5" t="s">
+      <c r="BV1" s="8" t="s">
         <v>68</v>
       </c>
       <c r="BW1" s="4" t="s">
@@ -1264,241 +1642,241 @@
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="18">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="M2" s="10" t="s">
+        <v>45788</v>
+      </c>
+      <c r="M2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="U2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="16">
+      <c r="V2" s="18">
         <f t="shared" ref="V2:V3" si="1">L2</f>
-        <v>45779</v>
-      </c>
-      <c r="W2" s="15" t="s">
+        <v>45788</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="Z2" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="19" t="s">
+      <c r="AB2" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AC2" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="20">
+      <c r="AD2" s="22">
         <v>35</v>
       </c>
-      <c r="AE2" s="21" t="s">
+      <c r="AE2" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AF2" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="AG2" s="22" t="s">
+      <c r="AG2" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AJ2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="AK2" s="23">
+      <c r="AK2" s="25">
         <f t="shared" ref="AK2:AK3" si="2">V2</f>
-        <v>45779</v>
-      </c>
-      <c r="AL2" s="23">
+        <v>45788</v>
+      </c>
+      <c r="AL2" s="25">
         <f t="shared" ref="AL2:AL3" si="3">V2</f>
-        <v>45779</v>
-      </c>
-      <c r="AM2" s="23">
+        <v>45788</v>
+      </c>
+      <c r="AM2" s="25">
         <f t="shared" ref="AM2:AM3" si="4">V2</f>
-        <v>45779</v>
-      </c>
-      <c r="AN2" s="16">
+        <v>45788</v>
+      </c>
+      <c r="AN2" s="18">
         <f t="shared" ref="AN2:AN3" si="5">AG2</f>
         <v>NaN</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AO2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AP2" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="AQ2" s="15" t="s">
+      <c r="AQ2" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AR2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AS2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AT2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AU2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AV2" s="23">
+      <c r="AV2" s="25">
         <f t="shared" ref="AV2:AV3" si="6">TODAY()+20</f>
-        <v>45830</v>
-      </c>
-      <c r="AW2" s="10" t="s">
+        <v>45839</v>
+      </c>
+      <c r="AW2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="AX2" s="24" t="s">
+      <c r="AX2" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="AY2" s="25" t="str">
+      <c r="AY2" s="27" t="str">
         <f>BB11</f>
-        <v>X4RQBABA57</v>
-      </c>
-      <c r="AZ2" s="23" t="s">
+        <v>X2RQBABA57</v>
+      </c>
+      <c r="AZ2" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="BA2" s="23" t="s">
+      <c r="BA2" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="BB2" s="11" t="s">
+      <c r="BB2" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="BC2" s="23" t="s">
+      <c r="BC2" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="BD2" s="26" t="s">
+      <c r="BD2" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="BE2" s="26" t="s">
+      <c r="BE2" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="BF2" s="26" t="s">
+      <c r="BF2" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="BG2" s="27" t="s">
+      <c r="BG2" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="23" t="s">
+      <c r="BH2" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="BI2" s="28" t="s">
+      <c r="BI2" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="BJ2" s="10" t="s">
+      <c r="BJ2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="BK2" s="29" t="s">
+      <c r="BK2" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BL2" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BM2" s="28" t="s">
+      <c r="BM2" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="BN2" s="10" t="s">
+      <c r="BN2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BO2" s="10" t="s">
+      <c r="BO2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BP2" s="10" t="s">
+      <c r="BP2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="10" t="s">
+      <c r="BQ2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="BR2" s="10" t="s">
+      <c r="BR2" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="BS2" s="10" t="s">
+      <c r="BS2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="BT2" s="10" t="s">
+      <c r="BT2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="BU2" s="10" t="s">
+      <c r="BU2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="BV2" s="30">
+      <c r="BV2" s="32">
         <f t="array" ref="BV2:BV3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>69719</v>
-      </c>
-      <c r="BW2" s="23">
+        <v>60306</v>
+      </c>
+      <c r="BW2" s="25">
         <v>44562</v>
       </c>
-      <c r="BX2" s="23">
+      <c r="BX2" s="25">
         <v>47119</v>
       </c>
-      <c r="BY2" s="15" t="s">
+      <c r="BY2" s="17" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1506,274 +1884,274 @@
       <c r="A3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="H3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="18">
         <f t="shared" si="0"/>
-        <v>45779</v>
-      </c>
-      <c r="M3" s="10" t="s">
+        <v>45788</v>
+      </c>
+      <c r="M3" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="T3" s="18" t="s">
+      <c r="T3" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="U3" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="V3" s="16">
+      <c r="V3" s="18">
         <f t="shared" si="1"/>
-        <v>45779</v>
-      </c>
-      <c r="W3" s="15" t="s">
+        <v>45788</v>
+      </c>
+      <c r="W3" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y3" s="11" t="s">
+      <c r="X3" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="Z3" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA3" s="11" t="s">
+      <c r="Z3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA3" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AB3" s="19" t="s">
+      <c r="AB3" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="AC3" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="AD3" s="20">
+      <c r="AC3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD3" s="22">
         <v>35</v>
       </c>
-      <c r="AE3" s="21" t="s">
+      <c r="AE3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="AF3" s="11" t="s">
+      <c r="AF3" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="AG3" s="22" t="s">
+      <c r="AG3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="AH3" s="15" t="s">
+      <c r="AH3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AI3" s="15" t="s">
+      <c r="AI3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AJ3" s="15" t="s">
+      <c r="AJ3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="AK3" s="23">
+      <c r="AK3" s="25">
         <f t="shared" si="2"/>
-        <v>45779</v>
-      </c>
-      <c r="AL3" s="23">
+        <v>45788</v>
+      </c>
+      <c r="AL3" s="25">
         <f t="shared" si="3"/>
-        <v>45779</v>
-      </c>
-      <c r="AM3" s="23">
+        <v>45788</v>
+      </c>
+      <c r="AM3" s="25">
         <f t="shared" si="4"/>
-        <v>45779</v>
-      </c>
-      <c r="AN3" s="16">
+        <v>45788</v>
+      </c>
+      <c r="AN3" s="18">
         <f t="shared" si="5"/>
         <v>NaN</v>
       </c>
-      <c r="AO3" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="AP3" s="15" t="s">
+      <c r="AO3" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="AQ3" s="15" t="s">
+      <c r="AP3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="AR3" s="15" t="s">
+      <c r="AR3" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="AS3" s="15" t="s">
+      <c r="AS3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AT3" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="AU3" s="10" t="s">
+      <c r="AT3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AV3" s="23">
+      <c r="AV3" s="25">
         <f t="shared" si="6"/>
-        <v>45830</v>
-      </c>
-      <c r="AW3" s="10" t="s">
+        <v>45839</v>
+      </c>
+      <c r="AW3" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="AX3" s="24" t="s">
+      <c r="AX3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="AY3" s="25" t="str">
+      <c r="AY3" s="27" t="str">
         <f>BB12</f>
-        <v>X5RQBABA24</v>
-      </c>
-      <c r="AZ3" s="23" t="s">
+        <v>X9RQBABA82</v>
+      </c>
+      <c r="AZ3" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="BA3" s="23" t="s">
+      <c r="BA3" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="BB3" s="11" t="s">
+      <c r="BB3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="BC3" s="23" t="s">
+      <c r="BC3" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="BD3" s="26" t="s">
+      <c r="BD3" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="BE3" s="26" t="s">
+      <c r="BE3" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="BF3" s="26" t="s">
+      <c r="BF3" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="BG3" s="27" t="s">
+      <c r="BG3" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="BH3" s="23" t="s">
+      <c r="BH3" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="BI3" s="28" t="s">
+      <c r="BI3" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="BJ3" s="10" t="s">
+      <c r="BJ3" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="BK3" s="29" t="s">
+      <c r="BK3" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="BL3" s="10" t="s">
+      <c r="BL3" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BM3" s="28" t="s">
+      <c r="BM3" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="BN3" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="BO3" s="10" t="s">
+      <c r="BN3" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="BO3" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BP3" s="10" t="s">
+      <c r="BP3" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BQ3" s="10" t="s">
+      <c r="BQ3" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="BR3" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="BS3" s="10" t="s">
+      <c r="BR3" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="BT3" s="10" t="s">
+      <c r="BS3" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="BT3" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="BU3" s="10" t="s">
+      <c r="BU3" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="BV3" s="30">
-        <v>29819</v>
-      </c>
-      <c r="BW3" s="23">
+      <c r="BV3" s="32">
+        <v>62675</v>
+      </c>
+      <c r="BW3" s="25">
         <v>44562</v>
       </c>
-      <c r="BX3" s="23">
+      <c r="BX3" s="25">
         <v>47119</v>
       </c>
-      <c r="BY3" s="15" t="s">
+      <c r="BY3" s="17" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4" ht="15.65" customHeight="1" spans="3:38" x14ac:dyDescent="0.25">
-      <c r="C4" s="8"/>
-      <c r="AL4" s="23"/>
+      <c r="C4" s="10"/>
+      <c r="AL4" s="25"/>
     </row>
     <row r="5" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C6" s="8"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" s="8"/>
+      <c r="C7" s="10"/>
     </row>
     <row r="8" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C8" s="8"/>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C9" s="8"/>
+      <c r="C9" s="10"/>
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C10" s="8"/>
+      <c r="C10" s="10"/>
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C11" s="8"/>
+      <c r="C11" s="10"/>
       <c r="AX11" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY11" s="2">
         <f t="array" ref="AY11:AY30">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BA11" s="2">
         <f t="array" ref="BA11:BA30">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
@@ -1781,317 +2159,317 @@
       </c>
       <c r="BB11" s="1" t="str">
         <f>AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X4RQBABA57</v>
+        <v>X2RQBABA57</v>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C12" s="8"/>
+      <c r="C12" s="10"/>
       <c r="AX12" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY12" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BA12" s="2">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="BB12" s="1" t="str">
         <f t="shared" ref="BB12:BB36" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X5RQBABA24</v>
+        <v>X9RQBABA82</v>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C13" s="8"/>
+      <c r="C13" s="10"/>
       <c r="AY13" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BA13" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="BB13" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>932</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C14" s="8"/>
+      <c r="C14" s="10"/>
       <c r="AX14" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY14" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BA14" s="2">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="BB14" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X585</v>
+        <v>X18</v>
       </c>
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
+      <c r="C15" s="10"/>
       <c r="AX15" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY15" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BA15" s="2">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="BB15" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X970</v>
+        <v>X48</v>
       </c>
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
+      <c r="C16" s="10"/>
       <c r="AX16" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY16" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA16" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB16" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X725</v>
+        <v>X526</v>
       </c>
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
+      <c r="C17" s="10"/>
       <c r="AX17" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY17" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA17" s="2">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="BB17" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X958</v>
+        <v>X697</v>
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C18" s="8"/>
+      <c r="C18" s="10"/>
       <c r="AX18" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY18" s="2">
         <v>9</v>
       </c>
       <c r="BA18" s="2">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="BB18" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X983</v>
+        <v>X912</v>
       </c>
     </row>
     <row r="19" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C19" s="8"/>
+      <c r="C19" s="10"/>
       <c r="AX19" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY19" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BA19" s="2">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="BB19" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X790</v>
+        <v>X123</v>
       </c>
     </row>
     <row r="20" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C20" s="8"/>
+      <c r="C20" s="10"/>
       <c r="AX20" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY20" s="2">
         <v>7</v>
       </c>
       <c r="BA20" s="2">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="BB20" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X78</v>
+        <v>X774</v>
       </c>
     </row>
     <row r="21" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C21" s="8"/>
+      <c r="C21" s="10"/>
       <c r="AX21" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY21" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA21" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="BB21" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X889</v>
+        <v>X988</v>
       </c>
     </row>
     <row r="22" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C22" s="8"/>
+      <c r="C22" s="10"/>
       <c r="AX22" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY22" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA22" s="2">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="BB22" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X78</v>
+        <v>X968</v>
       </c>
     </row>
     <row r="23" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C23" s="8"/>
+      <c r="C23" s="10"/>
       <c r="AX23" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY23" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BA23" s="2">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="BB23" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X658</v>
+        <v>X234</v>
       </c>
     </row>
     <row r="24" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C24" s="8"/>
+      <c r="C24" s="10"/>
       <c r="AX24" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY24" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA24" s="2">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="BB24" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X978</v>
+        <v>X562</v>
       </c>
     </row>
     <row r="25" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C25" s="8"/>
+      <c r="C25" s="10"/>
       <c r="AX25" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY25" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BA25" s="2">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="BB25" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X189</v>
+        <v>X728</v>
       </c>
     </row>
     <row r="26" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C26" s="8"/>
+      <c r="C26" s="10"/>
       <c r="AX26" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY26" s="2">
         <v>1</v>
       </c>
       <c r="BA26" s="2">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="BB26" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X140</v>
+        <v>X171</v>
       </c>
     </row>
     <row r="27" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C27" s="8"/>
+      <c r="C27" s="10"/>
       <c r="AX27" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY27" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BA27" s="2">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="BB27" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X251</v>
+        <v>X631</v>
       </c>
     </row>
     <row r="28" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C28" s="8"/>
+      <c r="C28" s="10"/>
       <c r="AX28" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY28" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BA28" s="2">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="BB28" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X522</v>
+        <v>X189</v>
       </c>
     </row>
     <row r="29" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C29" s="8"/>
+      <c r="C29" s="10"/>
       <c r="AX29" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY29" s="2">
         <v>5</v>
       </c>
       <c r="BA29" s="2">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="BB29" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X565</v>
+        <v>X532</v>
       </c>
     </row>
     <row r="30" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C30" s="8"/>
+      <c r="C30" s="10"/>
       <c r="AX30" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY30" s="2">
         <v>1</v>
       </c>
       <c r="BA30" s="2">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="BB30" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>X177</v>
+        <v>X169</v>
       </c>
     </row>
     <row r="31" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C31" s="8"/>
+      <c r="C31" s="10"/>
       <c r="AX31" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB31" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2099,9 +2477,9 @@
       </c>
     </row>
     <row r="32" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C32" s="8"/>
+      <c r="C32" s="10"/>
       <c r="AX32" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB32" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2109,9 +2487,9 @@
       </c>
     </row>
     <row r="33" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C33" s="8"/>
+      <c r="C33" s="10"/>
       <c r="AX33" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB33" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2119,9 +2497,9 @@
       </c>
     </row>
     <row r="34" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C34" s="8"/>
+      <c r="C34" s="10"/>
       <c r="AX34" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB34" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2129,9 +2507,9 @@
       </c>
     </row>
     <row r="35" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C35" s="8"/>
+      <c r="C35" s="10"/>
       <c r="AX35" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB35" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2139,7 +2517,7 @@
       </c>
     </row>
     <row r="36" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
+      <c r="C36" s="10"/>
       <c r="BB36" s="1">
         <f t="shared" si="7"/>
       </c>

--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -1,23 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D908E99F-48AF-4041-ADD1-5741D49BCE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="TestCaseIDs">Sheet2!$B$1:$BY$1</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="135">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -232,382 +247,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Elijah Ebert' Employee:{10699679}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('xpath=(//*[@data-automation-id=\'pex-search-result-header\']//a[contains(text(),\'10699679\')])[1]')[22m
-[2m  -   locator resolved to &lt;a data-uxi-rank="0" class="pexsearch-11mf54b" data…&gt;Elijah Ebert (10699679)&lt;/a&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not stable[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-uxi-widget-type="popup" data-uxi-popup-type…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>Passed</t>
   </si>
   <si>
     <t>221 Recruitment (Rivel Hehyte (10216960))</t>
@@ -619,10 +259,10 @@
     <t>Madame</t>
   </si>
   <si>
-    <t>Elijah</t>
-  </si>
-  <si>
-    <t>Ebert</t>
+    <t>Meredith</t>
+  </si>
+  <si>
+    <t>Ferry</t>
   </si>
   <si>
     <t>03 48 29 85 70</t>
@@ -757,22 +397,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699606</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Eldora</t>
-  </si>
-  <si>
-    <t>Thompson</t>
-  </si>
-  <si>
-    <t>Auto 75590546</t>
+    <t>Athena</t>
+  </si>
+  <si>
+    <t>Lesch</t>
+  </si>
+  <si>
+    <t>Auto 70256505</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -808,65 +442,65 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -878,13 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -901,7 +535,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -921,31 +555,53 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1324,11 +980,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:BY36"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BY36"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.90625" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.81640625" style="1" customWidth="1"/>
@@ -1405,7 +1062,7 @@
     <col min="77" max="77" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:77" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:77" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1638,237 +1295,237 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="9">
+        <v>10699756</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="J2" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="K2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="L2" s="18">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45796</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="18">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45788</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="P2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="Q2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="R2" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="S2" s="19" t="s">
+      <c r="T2" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="U2" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" s="18">
+        <f t="shared" ref="V2:V3" ca="1" si="1">L2</f>
+        <v>45796</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="U2" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="V2" s="18">
-        <f t="shared" ref="V2:V3" si="1">L2</f>
-        <v>45788</v>
-      </c>
-      <c r="W2" s="17" t="s">
+      <c r="X2" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="Y2" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Z2" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="AA2" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="13" t="s">
+      <c r="AB2" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="21" t="s">
+      <c r="AC2" s="21" t="s">
         <v>92</v>
-      </c>
-      <c r="AC2" s="21" t="s">
-        <v>93</v>
       </c>
       <c r="AD2" s="22">
         <v>35</v>
       </c>
       <c r="AE2" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF2" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AG2" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="AG2" s="24" t="s">
+      <c r="AH2" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AH2" s="17" t="s">
+      <c r="AI2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="17" t="s">
+      <c r="AJ2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AJ2" s="17" t="s">
+      <c r="AK2" s="25">
+        <f t="shared" ref="AK2:AK3" ca="1" si="2">V2</f>
+        <v>45796</v>
+      </c>
+      <c r="AL2" s="25">
+        <f t="shared" ref="AL2:AL3" ca="1" si="3">V2</f>
+        <v>45796</v>
+      </c>
+      <c r="AM2" s="25">
+        <f t="shared" ref="AM2:AM3" ca="1" si="4">V2</f>
+        <v>45796</v>
+      </c>
+      <c r="AN2" s="18" t="str">
+        <f t="shared" ref="AN2:AN3" si="5">AG2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AO2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="AK2" s="25">
-        <f t="shared" ref="AK2:AK3" si="2">V2</f>
-        <v>45788</v>
-      </c>
-      <c r="AL2" s="25">
-        <f t="shared" ref="AL2:AL3" si="3">V2</f>
-        <v>45788</v>
-      </c>
-      <c r="AM2" s="25">
-        <f t="shared" ref="AM2:AM3" si="4">V2</f>
-        <v>45788</v>
-      </c>
-      <c r="AN2" s="18">
-        <f t="shared" ref="AN2:AN3" si="5">AG2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AO2" s="17" t="s">
+      <c r="AP2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="AP2" s="17" t="s">
+      <c r="AQ2" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="AQ2" s="17" t="s">
+      <c r="AR2" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="AR2" s="17" t="s">
+      <c r="AS2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="AS2" s="17" t="s">
+      <c r="AT2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="12" t="s">
+      <c r="AU2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AV2" s="25">
+        <f t="shared" ref="AV2:AV3" ca="1" si="6">TODAY()+20</f>
+        <v>45847</v>
+      </c>
+      <c r="AW2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX2" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="AV2" s="25">
-        <f t="shared" ref="AV2:AV3" si="6">TODAY()+20</f>
-        <v>45839</v>
-      </c>
-      <c r="AW2" s="12" t="s">
+      <c r="AY2" s="27" t="str">
+        <f ca="1">BB11</f>
+        <v>X6RQBABA18</v>
+      </c>
+      <c r="AZ2" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="BA2" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB2" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="BC2" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE2" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF2" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="BG2" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="BH2" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="BI2" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="BJ2" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="BK2" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM2" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="AX2" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY2" s="27" t="str">
-        <f>BB11</f>
-        <v>X2RQBABA57</v>
-      </c>
-      <c r="AZ2" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA2" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB2" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="BC2" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="BF2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="BG2" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="BH2" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="BI2" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ2" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="BK2" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL2" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="BM2" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BN2" s="12" t="s">
+      <c r="BP2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BO2" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="BP2" s="12" t="s">
+      <c r="BQ2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="BR2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="BR2" s="12" t="s">
+      <c r="BS2" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="BT2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="BU2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="BT2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="BU2" s="12" t="s">
-        <v>119</v>
-      </c>
       <c r="BV2" s="32">
-        <f t="array" ref="BV2:BV3">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>60306</v>
+        <f t="array" aca="1" ref="BV2:BV3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
+        <v>17247</v>
       </c>
       <c r="BW2" s="25">
         <v>44562</v>
@@ -1877,239 +1534,240 @@
         <v>47119</v>
       </c>
       <c r="BY2" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:77" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="9">
+        <v>10699775</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="E3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="H3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="I3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>45796</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="P3" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="T3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U3" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="V3" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>45796</v>
+      </c>
+      <c r="W3" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="X3" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="Y3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="AA3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC3" s="21" t="s">
         <v>126</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="18">
-        <f t="shared" si="0"/>
-        <v>45788</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="P3" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="R3" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="S3" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="U3" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="V3" s="18">
-        <f t="shared" si="1"/>
-        <v>45788</v>
-      </c>
-      <c r="W3" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="X3" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y3" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z3" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA3" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC3" s="21" t="s">
-        <v>129</v>
       </c>
       <c r="AD3" s="22">
         <v>35</v>
       </c>
       <c r="AE3" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF3" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AF3" s="13" t="s">
+      <c r="AG3" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="AG3" s="24" t="s">
+      <c r="AH3" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AH3" s="17" t="s">
+      <c r="AI3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AI3" s="17" t="s">
+      <c r="AJ3" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AJ3" s="17" t="s">
-        <v>99</v>
-      </c>
       <c r="AK3" s="25">
-        <f t="shared" si="2"/>
-        <v>45788</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45796</v>
       </c>
       <c r="AL3" s="25">
-        <f t="shared" si="3"/>
-        <v>45788</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45796</v>
       </c>
       <c r="AM3" s="25">
-        <f t="shared" si="4"/>
-        <v>45788</v>
-      </c>
-      <c r="AN3" s="18">
+        <f t="shared" ca="1" si="4"/>
+        <v>45796</v>
+      </c>
+      <c r="AN3" s="18" t="str">
         <f t="shared" si="5"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AO3" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AP3" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ3" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="AR3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS3" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT3" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AU3" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV3" s="25">
+        <f t="shared" ca="1" si="6"/>
+        <v>45847</v>
+      </c>
+      <c r="AW3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX3" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="AY3" s="27" t="str">
+        <f ca="1">BB12</f>
+        <v>X8RQBABA54</v>
+      </c>
+      <c r="AZ3" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="BA3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="BC3" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD3" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="BG3" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="BH3" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="BI3" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="BJ3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="BK3" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="BL3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="BM3" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN3" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="AP3" s="17" t="s">
+      <c r="BO3" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="BP3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="BR3" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="AQ3" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR3" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AS3" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="AT3" s="12" t="s">
+      <c r="BS3" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="AU3" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV3" s="25">
-        <f t="shared" si="6"/>
-        <v>45839</v>
-      </c>
-      <c r="AW3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX3" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY3" s="27" t="str">
-        <f>BB12</f>
-        <v>X9RQBABA82</v>
-      </c>
-      <c r="AZ3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA3" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="BB3" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="BC3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD3" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="BE3" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="BF3" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="BG3" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="BH3" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="BI3" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ3" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="BK3" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="BM3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BN3" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO3" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="BP3" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="BQ3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="BR3" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="BS3" s="12" t="s">
-        <v>135</v>
-      </c>
       <c r="BT3" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BU3" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="BV3" s="32">
-        <v>62675</v>
+        <f ca="1"/>
+        <v>67513</v>
       </c>
       <c r="BW3" s="25">
         <v>44562</v>
@@ -2118,437 +1776,461 @@
         <v>47119</v>
       </c>
       <c r="BY3" s="17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" ht="15.65" customHeight="1" spans="3:38" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="10"/>
       <c r="AL4" s="25"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="10"/>
     </row>
-    <row r="7" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="10"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="10"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="10"/>
     </row>
-    <row r="10" ht="14.5" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="10"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="10"/>
       <c r="AX11" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY11" s="2">
-        <f t="array" ref="AY11:AY30">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>2</v>
+        <f t="array" aca="1" ref="AY11:AY30" ca="1">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
+        <v>6</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="BA11" s="2">
-        <f t="array" ref="BA11:BA30">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
-        <v>57</v>
+        <f t="array" aca="1" ref="BA11:BA30" ca="1">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
+        <v>18</v>
       </c>
       <c r="BB11" s="1" t="str">
-        <f>AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X2RQBABA57</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f ca="1">AX11&amp;AY11&amp;AZ11&amp;BA11</f>
+        <v>X6RQBABA18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="10"/>
       <c r="AX12" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY12" s="2">
-        <v>9</v>
+        <f ca="1"/>
+        <v>8</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="BA12" s="2">
-        <v>82</v>
+        <f ca="1"/>
+        <v>54</v>
       </c>
       <c r="BB12" s="1" t="str">
-        <f t="shared" ref="BB12:BB36" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X9RQBABA82</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BB12:BB36" ca="1" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
+        <v>X8RQBABA54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="10"/>
       <c r="AY13" s="2">
-        <v>3</v>
+        <f ca="1"/>
+        <v>2</v>
       </c>
       <c r="BA13" s="2">
-        <v>12</v>
+        <f ca="1"/>
+        <v>95</v>
       </c>
       <c r="BB13" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>312</v>
-      </c>
-    </row>
-    <row r="14" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="10"/>
       <c r="AX14" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY14" s="2">
-        <v>1</v>
+        <f ca="1"/>
+        <v>2</v>
       </c>
       <c r="BA14" s="2">
-        <v>8</v>
+        <f ca="1"/>
+        <v>43</v>
       </c>
       <c r="BB14" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X18</v>
-      </c>
-    </row>
-    <row r="15" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="10"/>
       <c r="AX15" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY15" s="2">
-        <v>4</v>
+        <f ca="1"/>
+        <v>7</v>
       </c>
       <c r="BA15" s="2">
-        <v>8</v>
+        <f ca="1"/>
+        <v>95</v>
       </c>
       <c r="BB15" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X48</v>
-      </c>
-    </row>
-    <row r="16" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X795</v>
+      </c>
+    </row>
+    <row r="16" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="10"/>
       <c r="AX16" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY16" s="2">
-        <v>5</v>
+        <f ca="1"/>
+        <v>1</v>
       </c>
       <c r="BA16" s="2">
-        <v>26</v>
+        <f ca="1"/>
+        <v>6</v>
       </c>
       <c r="BB16" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X526</v>
-      </c>
-    </row>
-    <row r="17" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X16</v>
+      </c>
+    </row>
+    <row r="17" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="10"/>
       <c r="AX17" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY17" s="2">
-        <v>6</v>
+        <f ca="1"/>
+        <v>8</v>
       </c>
       <c r="BA17" s="2">
-        <v>97</v>
+        <f ca="1"/>
+        <v>52</v>
       </c>
       <c r="BB17" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X697</v>
-      </c>
-    </row>
-    <row r="18" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X852</v>
+      </c>
+    </row>
+    <row r="18" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="10"/>
       <c r="AX18" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY18" s="2">
-        <v>9</v>
+        <f ca="1"/>
+        <v>2</v>
       </c>
       <c r="BA18" s="2">
-        <v>12</v>
+        <f ca="1"/>
+        <v>63</v>
       </c>
       <c r="BB18" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X912</v>
-      </c>
-    </row>
-    <row r="19" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X263</v>
+      </c>
+    </row>
+    <row r="19" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19" s="10"/>
       <c r="AX19" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY19" s="2">
-        <v>1</v>
+        <f ca="1"/>
+        <v>8</v>
       </c>
       <c r="BA19" s="2">
-        <v>23</v>
+        <f ca="1"/>
+        <v>94</v>
       </c>
       <c r="BB19" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X123</v>
-      </c>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X894</v>
+      </c>
+    </row>
+    <row r="20" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="10"/>
       <c r="AX20" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY20" s="2">
-        <v>7</v>
+        <f ca="1"/>
+        <v>3</v>
       </c>
       <c r="BA20" s="2">
-        <v>74</v>
+        <f ca="1"/>
+        <v>91</v>
       </c>
       <c r="BB20" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X774</v>
-      </c>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X391</v>
+      </c>
+    </row>
+    <row r="21" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21" s="10"/>
       <c r="AX21" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY21" s="2">
-        <v>9</v>
+        <f ca="1"/>
+        <v>4</v>
       </c>
       <c r="BA21" s="2">
-        <v>88</v>
+        <f ca="1"/>
+        <v>74</v>
       </c>
       <c r="BB21" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X988</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X474</v>
+      </c>
+    </row>
+    <row r="22" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C22" s="10"/>
       <c r="AX22" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY22" s="2">
-        <v>9</v>
+        <f ca="1"/>
+        <v>3</v>
       </c>
       <c r="BA22" s="2">
-        <v>68</v>
+        <f ca="1"/>
+        <v>5</v>
       </c>
       <c r="BB22" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X968</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X35</v>
+      </c>
+    </row>
+    <row r="23" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C23" s="10"/>
       <c r="AX23" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY23" s="2">
+        <f ca="1"/>
+        <v>6</v>
+      </c>
+      <c r="BA23" s="2">
+        <f ca="1"/>
         <v>2</v>
       </c>
-      <c r="BA23" s="2">
-        <v>34</v>
-      </c>
       <c r="BB23" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X234</v>
-      </c>
-    </row>
-    <row r="24" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X62</v>
+      </c>
+    </row>
+    <row r="24" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C24" s="10"/>
       <c r="AX24" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY24" s="2">
-        <v>5</v>
+        <f ca="1"/>
+        <v>1</v>
       </c>
       <c r="BA24" s="2">
-        <v>62</v>
+        <f ca="1"/>
+        <v>80</v>
       </c>
       <c r="BB24" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X562</v>
-      </c>
-    </row>
-    <row r="25" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X180</v>
+      </c>
+    </row>
+    <row r="25" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C25" s="10"/>
       <c r="AX25" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY25" s="2">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="BA25" s="2">
-        <v>28</v>
+        <f ca="1"/>
+        <v>82</v>
       </c>
       <c r="BB25" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X728</v>
-      </c>
-    </row>
-    <row r="26" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X782</v>
+      </c>
+    </row>
+    <row r="26" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="10"/>
       <c r="AX26" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY26" s="2">
-        <v>1</v>
+        <f ca="1"/>
+        <v>2</v>
       </c>
       <c r="BA26" s="2">
-        <v>71</v>
+        <f ca="1"/>
+        <v>77</v>
       </c>
       <c r="BB26" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X171</v>
-      </c>
-    </row>
-    <row r="27" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X277</v>
+      </c>
+    </row>
+    <row r="27" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="10"/>
       <c r="AX27" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY27" s="2">
-        <v>6</v>
+        <f ca="1"/>
+        <v>7</v>
       </c>
       <c r="BA27" s="2">
-        <v>31</v>
+        <f ca="1"/>
+        <v>39</v>
       </c>
       <c r="BB27" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X631</v>
-      </c>
-    </row>
-    <row r="28" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X739</v>
+      </c>
+    </row>
+    <row r="28" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="10"/>
       <c r="AX28" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY28" s="2">
-        <v>1</v>
+        <f ca="1"/>
+        <v>5</v>
       </c>
       <c r="BA28" s="2">
-        <v>89</v>
+        <f ca="1"/>
+        <v>58</v>
       </c>
       <c r="BB28" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X189</v>
-      </c>
-    </row>
-    <row r="29" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X558</v>
+      </c>
+    </row>
+    <row r="29" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C29" s="10"/>
       <c r="AX29" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY29" s="2">
-        <v>5</v>
+        <f ca="1"/>
+        <v>3</v>
       </c>
       <c r="BA29" s="2">
-        <v>32</v>
+        <f ca="1"/>
+        <v>92</v>
       </c>
       <c r="BB29" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X532</v>
-      </c>
-    </row>
-    <row r="30" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X392</v>
+      </c>
+    </row>
+    <row r="30" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="10"/>
       <c r="AX30" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AY30" s="2">
-        <v>1</v>
+        <f ca="1"/>
+        <v>2</v>
       </c>
       <c r="BA30" s="2">
-        <v>69</v>
+        <f ca="1"/>
+        <v>70</v>
       </c>
       <c r="BB30" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>X169</v>
-      </c>
-    </row>
-    <row r="31" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>X270</v>
+      </c>
+    </row>
+    <row r="31" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C31" s="10"/>
       <c r="AX31" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BB31" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C32" s="10"/>
       <c r="AX32" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BB32" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="10"/>
       <c r="AX33" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BB33" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C34" s="10"/>
       <c r="AX34" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BB34" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="10"/>
       <c r="AX35" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BB35" s="1" t="str">
         <f t="shared" si="7"/>
         <v>X</v>
       </c>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C36" s="10"/>
-      <c r="BB36" s="1">
+      <c r="BB36" s="1" t="str">
         <f t="shared" si="7"/>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AJ3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AJ3 W2:W3 U2:U3 R2:R3 K2:K3 BL2:BL3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="T2" r:id="rId1"/>
-    <hyperlink ref="T3" r:id="rId2"/>
+    <hyperlink ref="T2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="T3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D908E99F-48AF-4041-ADD1-5741D49BCE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC10860-08F1-41C5-8072-CA959288F769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,7 +14,6 @@
     <definedName name="TestCaseIDs">Sheet2!$B$1:$BY$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="136">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -247,166 +246,169 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>221 Recruitment (Rivel Hehyte (10216960))</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Madame</t>
+  </si>
+  <si>
+    <t>Leanne</t>
+  </si>
+  <si>
+    <t>Ernser</t>
+  </si>
+  <si>
+    <t>03 48 29 85 70</t>
+  </si>
+  <si>
+    <t>Landline</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Nord-Pas-de-Calais</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>59700</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>Test@email.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Retail Assistant</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>221 Paris-Villeneuve La Garenne</t>
+  </si>
+  <si>
+    <t>Hourly</t>
+  </si>
+  <si>
+    <t>Employe@5 - Jeudi - (Contracted Days of the Week (France)-France)</t>
+  </si>
+  <si>
+    <t>5 jours (France)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>CDI (Permanent)</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>CDI (Aucune raison nécessaire)</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>Collective Agreement - France</t>
+  </si>
+  <si>
+    <t>Agent de Maîtrise</t>
+  </si>
+  <si>
+    <t>AM1</t>
+  </si>
+  <si>
+    <t>France Retail Assistant &gt;=1yr Exp</t>
+  </si>
+  <si>
+    <t>1yr Exp. or Diploma</t>
+  </si>
+  <si>
+    <t>National Identity Card (CNI)</t>
+  </si>
+  <si>
+    <t>01/01/1999</t>
+  </si>
+  <si>
+    <t>01/01/2045</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Celibataire</t>
+  </si>
+  <si>
+    <t>BNPAFRPPTAS</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>FR1420041010050500013M02606</t>
+  </si>
+  <si>
+    <t>GrunB FrunB</t>
+  </si>
+  <si>
+    <t>Maiden</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>Senger</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>FR Monthly</t>
+  </si>
+  <si>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t>10700388</t>
+  </si>
+  <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>221 Recruitment (Rivel Hehyte (10216960))</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Madame</t>
-  </si>
-  <si>
-    <t>Meredith</t>
-  </si>
-  <si>
-    <t>Ferry</t>
-  </si>
-  <si>
-    <t>03 48 29 85 70</t>
-  </si>
-  <si>
-    <t>Landline</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Nord-Pas-de-Calais</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>59700</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>Test@email.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Retail Assistant</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>221 Paris-Villeneuve La Garenne</t>
-  </si>
-  <si>
-    <t>Hourly</t>
-  </si>
-  <si>
-    <t>Employe@5 - Jeudi - (Contracted Days of the Week (France)-France)</t>
-  </si>
-  <si>
-    <t>5 jours (France)</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>CDI (Permanent)</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>CDI (Aucune raison nécessaire)</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>Collective Agreement - France</t>
-  </si>
-  <si>
-    <t>Agent de Maîtrise</t>
-  </si>
-  <si>
-    <t>AM1</t>
-  </si>
-  <si>
-    <t>France Retail Assistant &gt;=1yr Exp</t>
-  </si>
-  <si>
-    <t>1yr Exp. or Diploma</t>
-  </si>
-  <si>
-    <t>National Identity Card (CNI)</t>
-  </si>
-  <si>
-    <t>01/01/1999</t>
-  </si>
-  <si>
-    <t>01/01/2045</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Celibataire</t>
-  </si>
-  <si>
-    <t>BNPAFRPPTAS</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>FR1420041010050500013M02606</t>
-  </si>
-  <si>
-    <t>GrunB FrunB</t>
-  </si>
-  <si>
-    <t>Maiden</t>
-  </si>
-  <si>
-    <t>Anthony</t>
-  </si>
-  <si>
-    <t>Senger</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>FR Monthly</t>
-  </si>
-  <si>
-    <t>Test_2</t>
-  </si>
-  <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Athena</t>
-  </si>
-  <si>
-    <t>Lesch</t>
-  </si>
-  <si>
-    <t>Auto 70256505</t>
+    <t>Petra</t>
+  </si>
+  <si>
+    <t>Gottlieb</t>
+  </si>
+  <si>
+    <t>Auto 12065883</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -1299,233 +1301,229 @@
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="9">
-        <v>10699756</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="J2" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="K2" s="17" t="s">
         <v>78</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="L2" s="18">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="P2" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="Q2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="R2" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S2" s="19" t="s">
+      <c r="T2" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="20" t="s">
-        <v>85</v>
-      </c>
       <c r="U2" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V2" s="18">
         <f t="shared" ref="V2:V3" ca="1" si="1">L2</f>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="W2" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="X2" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="Y2" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Z2" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="AA2" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="AA2" s="13" t="s">
+      <c r="AB2" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="21" t="s">
+      <c r="AC2" s="21" t="s">
         <v>91</v>
-      </c>
-      <c r="AC2" s="21" t="s">
-        <v>92</v>
       </c>
       <c r="AD2" s="22">
         <v>35</v>
       </c>
       <c r="AE2" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF2" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AG2" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="AG2" s="24" t="s">
+      <c r="AH2" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="AH2" s="17" t="s">
+      <c r="AI2" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AI2" s="17" t="s">
+      <c r="AJ2" s="17" t="s">
         <v>97</v>
-      </c>
-      <c r="AJ2" s="17" t="s">
-        <v>98</v>
       </c>
       <c r="AK2" s="25">
         <f t="shared" ref="AK2:AK3" ca="1" si="2">V2</f>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="AL2" s="25">
         <f t="shared" ref="AL2:AL3" ca="1" si="3">V2</f>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="AM2" s="25">
         <f t="shared" ref="AM2:AM3" ca="1" si="4">V2</f>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="AN2" s="18" t="str">
         <f t="shared" ref="AN2:AN3" si="5">AG2</f>
         <v>N/A</v>
       </c>
       <c r="AO2" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AP2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="AP2" s="17" t="s">
+      <c r="AQ2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="AQ2" s="17" t="s">
+      <c r="AR2" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="AR2" s="17" t="s">
+      <c r="AS2" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="AS2" s="17" t="s">
+      <c r="AT2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AT2" s="12" t="s">
+      <c r="AU2" s="12" t="s">
         <v>104</v>
-      </c>
-      <c r="AU2" s="12" t="s">
-        <v>105</v>
       </c>
       <c r="AV2" s="25">
         <f t="shared" ref="AV2:AV3" ca="1" si="6">TODAY()+20</f>
-        <v>45847</v>
+        <v>45886</v>
       </c>
       <c r="AW2" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AX2" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AY2" s="27" t="str">
         <f ca="1">BB11</f>
-        <v>X6RQBABA18</v>
+        <v>X7RQBABA26</v>
       </c>
       <c r="AZ2" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="BA2" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="BA2" s="25" t="s">
+      <c r="BB2" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="BB2" s="13" t="s">
+      <c r="BC2" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD2" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE2" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="BF2" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="BG2" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="BC2" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="BD2" s="28" t="s">
+      <c r="BH2" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI2" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="BK2" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL2" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM2" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN2" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO2" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="BE2" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="BF2" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="BG2" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH2" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="BI2" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="BJ2" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="BK2" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL2" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="BM2" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="BN2" s="12" t="s">
+      <c r="BP2" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="BO2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP2" s="12" t="s">
+      <c r="BQ2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="BR2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BQ2" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="BR2" s="12" t="s">
+      <c r="BS2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="BT2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="BU2" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="BT2" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="BU2" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="BV2" s="32">
         <f t="array" aca="1" ref="BV2:BV3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>17247</v>
+        <v>87595</v>
       </c>
       <c r="BW2" s="25">
         <v>44562</v>
@@ -1534,240 +1532,240 @@
         <v>47119</v>
       </c>
       <c r="BY2" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="9">
-        <v>10699775</v>
-      </c>
       <c r="C3" s="10" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="G3" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>78</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>79</v>
       </c>
       <c r="L3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N3" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="P3" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="Q3" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="R3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="S3" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="R3" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S3" s="19" t="s">
+      <c r="T3" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="T3" s="20" t="s">
-        <v>85</v>
-      </c>
       <c r="U3" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V3" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X3" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Y3" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z3" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AA3" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB3" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="AB3" s="21" t="s">
-        <v>91</v>
-      </c>
       <c r="AC3" s="21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD3" s="22">
         <v>35</v>
       </c>
       <c r="AE3" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AF3" s="13" t="s">
+      <c r="AG3" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="AG3" s="24" t="s">
+      <c r="AH3" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="AH3" s="17" t="s">
+      <c r="AI3" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AI3" s="17" t="s">
+      <c r="AJ3" s="17" t="s">
         <v>97</v>
-      </c>
-      <c r="AJ3" s="17" t="s">
-        <v>98</v>
       </c>
       <c r="AK3" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="AL3" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="AM3" s="25">
         <f t="shared" ca="1" si="4"/>
-        <v>45796</v>
+        <v>45835</v>
       </c>
       <c r="AN3" s="18" t="str">
         <f t="shared" si="5"/>
         <v>N/A</v>
       </c>
       <c r="AO3" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP3" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AQ3" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR3" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="AR3" s="17" t="s">
+      <c r="AS3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="AS3" s="17" t="s">
-        <v>103</v>
-      </c>
       <c r="AT3" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AU3" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AV3" s="25">
         <f t="shared" ca="1" si="6"/>
-        <v>45847</v>
+        <v>45886</v>
       </c>
       <c r="AW3" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AX3" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AY3" s="27" t="str">
         <f ca="1">BB12</f>
-        <v>X8RQBABA54</v>
+        <v>X5RQBABA80</v>
       </c>
       <c r="AZ3" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="BA3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="BA3" s="25" t="s">
+      <c r="BB3" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="BB3" s="13" t="s">
+      <c r="BC3" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD3" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE3" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="BF3" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="BG3" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="BC3" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="BD3" s="28" t="s">
+      <c r="BH3" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI3" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ3" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="BK3" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL3" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN3" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="BO3" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="BE3" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="BF3" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="BG3" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH3" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="BI3" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="BJ3" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="BK3" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL3" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="BM3" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="BN3" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="BO3" s="12" t="s">
-        <v>74</v>
-      </c>
       <c r="BP3" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="BQ3" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="BR3" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BS3" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BT3" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="BU3" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BV3" s="32">
         <f ca="1"/>
-        <v>67513</v>
+        <v>75777</v>
       </c>
       <c r="BW3" s="25">
         <v>44562</v>
@@ -1776,7 +1774,7 @@
         <v>47119</v>
       </c>
       <c r="BY3" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:77" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
@@ -1802,82 +1800,82 @@
     <row r="11" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="10"/>
       <c r="AX11" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY11" s="2">
         <f t="array" aca="1" ref="AY11:AY30" ca="1">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ11" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BA11" s="2">
         <f t="array" aca="1" ref="BA11:BA30" ca="1">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BB11" s="1" t="str">
         <f ca="1">AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X6RQBABA18</v>
+        <v>X7RQBABA26</v>
       </c>
     </row>
     <row r="12" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="10"/>
       <c r="AX12" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY12" s="2">
         <f ca="1"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ12" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BA12" s="2">
         <f ca="1"/>
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BB12" s="1" t="str">
         <f t="shared" ref="BB12:BB36" ca="1" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X8RQBABA54</v>
+        <v>X5RQBABA80</v>
       </c>
     </row>
     <row r="13" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="10"/>
       <c r="AY13" s="2">
         <f ca="1"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BA13" s="2">
         <f ca="1"/>
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="BB13" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>295</v>
+        <v>786</v>
       </c>
     </row>
     <row r="14" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="10"/>
       <c r="AX14" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY14" s="2">
         <f ca="1"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BA14" s="2">
         <f ca="1"/>
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="BB14" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X243</v>
+        <v>X736</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="10"/>
       <c r="AX15" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY15" s="2">
         <f ca="1"/>
@@ -1885,35 +1883,35 @@
       </c>
       <c r="BA15" s="2">
         <f ca="1"/>
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="BB15" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X795</v>
+        <v>X751</v>
       </c>
     </row>
     <row r="16" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="10"/>
       <c r="AX16" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY16" s="2">
         <f ca="1"/>
+        <v>6</v>
+      </c>
+      <c r="BA16" s="2">
+        <f ca="1"/>
         <v>1</v>
-      </c>
-      <c r="BA16" s="2">
-        <f ca="1"/>
-        <v>6</v>
       </c>
       <c r="BB16" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X16</v>
+        <v>X61</v>
       </c>
     </row>
     <row r="17" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="10"/>
       <c r="AX17" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY17" s="2">
         <f ca="1"/>
@@ -1921,233 +1919,233 @@
       </c>
       <c r="BA17" s="2">
         <f ca="1"/>
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="BB17" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X852</v>
-      </c>
-    </row>
-    <row r="18" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>X877</v>
+      </c>
+    </row>
+    <row r="18" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C18" s="10"/>
       <c r="AX18" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY18" s="2">
         <f ca="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BA18" s="2">
         <f ca="1"/>
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="BB18" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X263</v>
+        <v>X895</v>
       </c>
     </row>
     <row r="19" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19" s="10"/>
       <c r="AX19" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY19" s="2">
         <f ca="1"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BA19" s="2">
         <f ca="1"/>
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="BB19" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X894</v>
+        <v>X23</v>
       </c>
     </row>
     <row r="20" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="10"/>
       <c r="AX20" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY20" s="2">
         <f ca="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA20" s="2">
         <f ca="1"/>
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="BB20" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X391</v>
+        <v>X549</v>
       </c>
     </row>
     <row r="21" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21" s="10"/>
       <c r="AX21" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY21" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA21" s="2">
         <f ca="1"/>
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="BB21" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X474</v>
+        <v>X868</v>
       </c>
     </row>
     <row r="22" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C22" s="10"/>
       <c r="AX22" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY22" s="2">
         <f ca="1"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BA22" s="2">
         <f ca="1"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BB22" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X35</v>
+        <v>X715</v>
       </c>
     </row>
     <row r="23" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C23" s="10"/>
       <c r="AX23" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY23" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BA23" s="2">
         <f ca="1"/>
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="BB23" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X62</v>
+        <v>X297</v>
       </c>
     </row>
     <row r="24" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C24" s="10"/>
       <c r="AX24" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY24" s="2">
         <f ca="1"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BA24" s="2">
         <f ca="1"/>
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="BB24" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X180</v>
+        <v>X822</v>
       </c>
     </row>
     <row r="25" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C25" s="10"/>
       <c r="AX25" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY25" s="2">
         <f ca="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA25" s="2">
         <f ca="1"/>
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="BB25" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X782</v>
+        <v>X65</v>
       </c>
     </row>
     <row r="26" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="10"/>
       <c r="AX26" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY26" s="2">
         <f ca="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA26" s="2">
         <f ca="1"/>
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="BB26" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X277</v>
+        <v>X150</v>
       </c>
     </row>
     <row r="27" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="10"/>
       <c r="AX27" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY27" s="2">
         <f ca="1"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA27" s="2">
         <f ca="1"/>
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="BB27" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X739</v>
+        <v>X41</v>
       </c>
     </row>
     <row r="28" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="10"/>
       <c r="AX28" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY28" s="2">
         <f ca="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA28" s="2">
         <f ca="1"/>
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="BB28" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X558</v>
+        <v>X952</v>
       </c>
     </row>
     <row r="29" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C29" s="10"/>
       <c r="AX29" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY29" s="2">
         <f ca="1"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BA29" s="2">
         <f ca="1"/>
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="BB29" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X392</v>
+        <v>X823</v>
       </c>
     </row>
     <row r="30" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="10"/>
       <c r="AX30" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY30" s="2">
         <f ca="1"/>
@@ -2155,17 +2153,17 @@
       </c>
       <c r="BA30" s="2">
         <f ca="1"/>
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BB30" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X270</v>
+        <v>X240</v>
       </c>
     </row>
     <row r="31" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C31" s="10"/>
       <c r="AX31" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB31" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2175,7 +2173,7 @@
     <row r="32" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C32" s="10"/>
       <c r="AX32" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB32" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2185,7 +2183,7 @@
     <row r="33" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="10"/>
       <c r="AX33" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB33" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2195,7 +2193,7 @@
     <row r="34" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C34" s="10"/>
       <c r="AX34" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB34" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2205,7 +2203,7 @@
     <row r="35" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="10"/>
       <c r="AX35" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB35" s="1" t="str">
         <f t="shared" si="7"/>
@@ -2230,7 +2228,7 @@
     <hyperlink ref="T3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId3"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_France_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{99C052E4-845A-49AD-8442-097F3093245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{DEF63143-068F-45C4-947F-9DE8745CBB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,10 +256,10 @@
     <t>Madame</t>
   </si>
   <si>
-    <t>Christ</t>
-  </si>
-  <si>
-    <t>Wunsch</t>
+    <t>Morton</t>
+  </si>
+  <si>
+    <t>Wyman</t>
   </si>
   <si>
     <t>03 48 29 85 70</t>
@@ -397,13 +397,13 @@
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Francisco</t>
-  </si>
-  <si>
-    <t>MacGyver</t>
-  </si>
-  <si>
-    <t>Auto 41715071</t>
+    <t>Norene</t>
+  </si>
+  <si>
+    <t>Tromp</t>
+  </si>
+  <si>
+    <t>Auto 23126512</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -503,7 +503,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -541,7 +541,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,7 +620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -708,6 +714,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -990,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BY36"/>
+  <dimension ref="A1:BY38"/>
   <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
@@ -1309,9 +1318,9 @@
         <v>70</v>
       </c>
       <c r="B2" s="9">
-        <v>10700240</v>
-      </c>
-      <c r="C2" s="33" t="s">
+        <v>10700449</v>
+      </c>
+      <c r="C2" s="34" t="s">
         <v>134</v>
       </c>
       <c r="D2" s="11" t="s">
@@ -1340,7 +1349,7 @@
       </c>
       <c r="L2" s="18">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>72</v>
@@ -1371,7 +1380,7 @@
       </c>
       <c r="V2" s="18">
         <f t="shared" ref="V2:V3" ca="1" si="1">L2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="W2" s="17" t="s">
         <v>85</v>
@@ -1417,15 +1426,15 @@
       </c>
       <c r="AK2" s="25">
         <f t="shared" ref="AK2:AK3" ca="1" si="2">V2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL2" s="25">
         <f t="shared" ref="AL2:AL3" ca="1" si="3">V2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM2" s="25">
         <f t="shared" ref="AM2:AM3" ca="1" si="4">V2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AN2" s="18" t="str">
         <f t="shared" ref="AN2:AN3" si="5">AG2</f>
@@ -1454,7 +1463,7 @@
       </c>
       <c r="AV2" s="25">
         <f t="shared" ref="AV2:AV3" ca="1" si="6">TODAY()+20</f>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="AW2" s="12" t="s">
         <v>72</v>
@@ -1464,7 +1473,7 @@
       </c>
       <c r="AY2" s="27" t="str">
         <f ca="1">BB11</f>
-        <v>X2RQBABA76</v>
+        <v>X7RQBABA84</v>
       </c>
       <c r="AZ2" s="25" t="s">
         <v>106</v>
@@ -1534,7 +1543,7 @@
       </c>
       <c r="BV2" s="32">
         <f t="array" aca="1" ref="BV2:BV3" ca="1">_xlfn.RANDARRAY(2,1,12345,99999,TRUE)</f>
-        <v>71467</v>
+        <v>62852</v>
       </c>
       <c r="BW2" s="25">
         <v>44562</v>
@@ -1551,9 +1560,9 @@
         <v>119</v>
       </c>
       <c r="B3" s="9">
-        <v>10700243</v>
-      </c>
-      <c r="C3" s="33" t="s">
+        <v>10700450</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>134</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -1582,7 +1591,7 @@
       </c>
       <c r="L3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>72</v>
@@ -1613,7 +1622,7 @@
       </c>
       <c r="V3" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="W3" s="17" t="s">
         <v>85</v>
@@ -1659,15 +1668,15 @@
       </c>
       <c r="AK3" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AL3" s="25">
         <f t="shared" ca="1" si="3"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AM3" s="25">
         <f t="shared" ca="1" si="4"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="AN3" s="18" t="str">
         <f t="shared" si="5"/>
@@ -1696,7 +1705,7 @@
       </c>
       <c r="AV3" s="25">
         <f t="shared" ca="1" si="6"/>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="AW3" s="12" t="s">
         <v>72</v>
@@ -1706,7 +1715,7 @@
       </c>
       <c r="AY3" s="27" t="str">
         <f ca="1">BB12</f>
-        <v>X7RQBABA45</v>
+        <v>X4RQBABA51</v>
       </c>
       <c r="AZ3" s="25" t="s">
         <v>106</v>
@@ -1776,7 +1785,7 @@
       </c>
       <c r="BV3" s="32">
         <f ca="1"/>
-        <v>78129</v>
+        <v>63510</v>
       </c>
       <c r="BW3" s="25">
         <v>44562</v>
@@ -1794,205 +1803,205 @@
     </row>
     <row r="5" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="10"/>
+      <c r="C6" s="33"/>
     </row>
     <row r="7" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="10"/>
+      <c r="C7" s="33"/>
     </row>
     <row r="8" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="10"/>
+      <c r="C8" s="33"/>
     </row>
     <row r="9" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="10"/>
+      <c r="C9" s="33"/>
     </row>
     <row r="10" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="10"/>
+      <c r="C10" s="33"/>
     </row>
     <row r="11" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="10"/>
+      <c r="C11" s="33"/>
       <c r="AX11" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY11" s="2">
         <f t="array" aca="1" ref="AY11:AY30" ca="1">_xlfn.RANDARRAY(20,1,1,9,TRUE)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AZ11" s="1" t="s">
         <v>133</v>
       </c>
       <c r="BA11" s="2">
         <f t="array" aca="1" ref="BA11:BA30" ca="1">_xlfn.RANDARRAY(20,1,1,99,TRUE)</f>
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BB11" s="1" t="str">
         <f ca="1">AX11&amp;AY11&amp;AZ11&amp;BA11</f>
-        <v>X2RQBABA76</v>
+        <v>X7RQBABA84</v>
       </c>
     </row>
     <row r="12" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="10"/>
+      <c r="C12" s="33"/>
       <c r="AX12" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY12" s="2">
         <f ca="1"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ12" s="1" t="s">
         <v>133</v>
       </c>
       <c r="BA12" s="2">
         <f ca="1"/>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="BB12" s="1" t="str">
         <f t="shared" ref="BB12:BB36" ca="1" si="7">AX12&amp;AY12&amp;AZ12&amp;BA12</f>
-        <v>X7RQBABA45</v>
+        <v>X4RQBABA51</v>
       </c>
     </row>
     <row r="13" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="10"/>
+      <c r="C13" s="33"/>
       <c r="AY13" s="2">
         <f ca="1"/>
         <v>5</v>
       </c>
       <c r="BA13" s="2">
         <f ca="1"/>
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="BB13" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>571</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="10"/>
+      <c r="C14" s="33"/>
       <c r="AX14" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY14" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA14" s="2">
         <f ca="1"/>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="BB14" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X496</v>
+        <v>X180</v>
       </c>
     </row>
     <row r="15" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="10"/>
+      <c r="C15" s="33"/>
       <c r="AX15" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY15" s="2">
         <f ca="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA15" s="2">
         <f ca="1"/>
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="BB15" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X870</v>
+        <v>X782</v>
       </c>
     </row>
     <row r="16" spans="1:77" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="10"/>
+      <c r="C16" s="33"/>
       <c r="AX16" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY16" s="2">
         <f ca="1"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BA16" s="2">
         <f ca="1"/>
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="BB16" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X943</v>
+        <v>X111</v>
       </c>
     </row>
     <row r="17" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="10"/>
+      <c r="C17" s="33"/>
       <c r="AX17" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY17" s="2">
         <f ca="1"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BA17" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="BB17" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X14</v>
+        <v>X877</v>
       </c>
     </row>
     <row r="18" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="10"/>
+      <c r="C18" s="33"/>
       <c r="AX18" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY18" s="2">
         <f ca="1"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BA18" s="2">
         <f ca="1"/>
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="BB18" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X396</v>
+        <v>X933</v>
       </c>
     </row>
     <row r="19" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C19" s="10"/>
+      <c r="C19" s="33"/>
       <c r="AX19" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY19" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA19" s="2">
         <f ca="1"/>
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="BB19" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X439</v>
+        <v>X73</v>
       </c>
     </row>
     <row r="20" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="10"/>
+      <c r="C20" s="33"/>
       <c r="AX20" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY20" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BA20" s="2">
         <f ca="1"/>
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="BB20" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X669</v>
+        <v>X159</v>
       </c>
     </row>
     <row r="21" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="10"/>
+      <c r="C21" s="33"/>
       <c r="AX21" s="1" t="s">
         <v>132</v>
       </c>
@@ -2002,15 +2011,15 @@
       </c>
       <c r="BA21" s="2">
         <f ca="1"/>
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="BB21" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X169</v>
+        <v>X191</v>
       </c>
     </row>
     <row r="22" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="10"/>
+      <c r="C22" s="33"/>
       <c r="AX22" s="1" t="s">
         <v>132</v>
       </c>
@@ -2020,69 +2029,69 @@
       </c>
       <c r="BA22" s="2">
         <f ca="1"/>
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="BB22" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X873</v>
+        <v>X820</v>
       </c>
     </row>
     <row r="23" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="10"/>
+      <c r="C23" s="33"/>
       <c r="AX23" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY23" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BA23" s="2">
         <f ca="1"/>
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="BB23" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X627</v>
+        <v>X170</v>
       </c>
     </row>
     <row r="24" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="10"/>
+      <c r="C24" s="33"/>
       <c r="AX24" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY24" s="2">
         <f ca="1"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BA24" s="2">
         <f ca="1"/>
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="BB24" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X857</v>
+        <v>X169</v>
       </c>
     </row>
     <row r="25" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="10"/>
+      <c r="C25" s="33"/>
       <c r="AX25" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY25" s="2">
         <f ca="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA25" s="2">
         <f ca="1"/>
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="BB25" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X747</v>
+        <v>X987</v>
       </c>
     </row>
     <row r="26" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C26" s="10"/>
+      <c r="C26" s="33"/>
       <c r="AX26" s="1" t="s">
         <v>132</v>
       </c>
@@ -2092,87 +2101,87 @@
       </c>
       <c r="BA26" s="2">
         <f ca="1"/>
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="BB26" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X194</v>
+        <v>X111</v>
       </c>
     </row>
     <row r="27" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="10"/>
+      <c r="C27" s="33"/>
       <c r="AX27" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY27" s="2">
         <f ca="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA27" s="2">
         <f ca="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BB27" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X45</v>
+        <v>X812</v>
       </c>
     </row>
     <row r="28" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C28" s="10"/>
+      <c r="C28" s="33"/>
       <c r="AX28" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY28" s="2">
         <f ca="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BA28" s="2">
         <f ca="1"/>
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="BB28" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X551</v>
+        <v>X227</v>
       </c>
     </row>
     <row r="29" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="10"/>
+      <c r="C29" s="33"/>
       <c r="AX29" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY29" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BA29" s="2">
         <f ca="1"/>
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="BB29" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X660</v>
+        <v>X186</v>
       </c>
     </row>
     <row r="30" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C30" s="10"/>
+      <c r="C30" s="33"/>
       <c r="AX30" s="1" t="s">
         <v>132</v>
       </c>
       <c r="AY30" s="2">
         <f ca="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA30" s="2">
         <f ca="1"/>
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="BB30" s="1" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>X651</v>
+        <v>X828</v>
       </c>
     </row>
     <row r="31" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C31" s="10"/>
+      <c r="C31" s="33"/>
       <c r="AX31" s="1" t="s">
         <v>132</v>
       </c>
@@ -2182,7 +2191,7 @@
       </c>
     </row>
     <row r="32" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="10"/>
+      <c r="C32" s="33"/>
       <c r="AX32" s="1" t="s">
         <v>132</v>
       </c>
@@ -2192,7 +2201,7 @@
       </c>
     </row>
     <row r="33" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="10"/>
+      <c r="C33" s="33"/>
       <c r="AX33" s="1" t="s">
         <v>132</v>
       </c>
@@ -2202,7 +2211,7 @@
       </c>
     </row>
     <row r="34" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C34" s="10"/>
+      <c r="C34" s="33"/>
       <c r="AX34" s="1" t="s">
         <v>132</v>
       </c>
@@ -2212,7 +2221,7 @@
       </c>
     </row>
     <row r="35" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="10"/>
+      <c r="C35" s="33"/>
       <c r="AX35" s="1" t="s">
         <v>132</v>
       </c>
@@ -2222,11 +2231,17 @@
       </c>
     </row>
     <row r="36" spans="3:54" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="10"/>
+      <c r="C36" s="33"/>
       <c r="BB36" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
+    </row>
+    <row r="37" spans="3:54" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="33"/>
+    </row>
+    <row r="38" spans="3:54" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="33"/>
     </row>
   </sheetData>
   <dataValidations count="1">
